--- a/volume/output_manual.xlsx
+++ b/volume/output_manual.xlsx
@@ -3151,6 +3151,9 @@
       <c r="P52" t="str">
         <v>Add</v>
       </c>
+      <c r="Q52" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
@@ -3201,6 +3204,9 @@
       <c r="P53" t="str">
         <v>Add</v>
       </c>
+      <c r="Q53" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
@@ -3251,6 +3257,9 @@
       <c r="P54" t="str">
         <v>Add</v>
       </c>
+      <c r="Q54" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
@@ -3301,6 +3310,9 @@
       <c r="P55" t="str">
         <v>Add</v>
       </c>
+      <c r="Q55" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
@@ -3351,6 +3363,9 @@
       <c r="P56" t="str">
         <v>Add</v>
       </c>
+      <c r="Q56" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
@@ -3401,6 +3416,9 @@
       <c r="P57" t="str">
         <v>Add</v>
       </c>
+      <c r="Q57" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
@@ -3451,6 +3469,9 @@
       <c r="P58" t="str">
         <v>Add</v>
       </c>
+      <c r="Q58" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
@@ -3501,6 +3522,9 @@
       <c r="P59" t="str">
         <v>Add</v>
       </c>
+      <c r="Q59" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
@@ -3551,6 +3575,9 @@
       <c r="P60" t="str">
         <v>Add</v>
       </c>
+      <c r="Q60" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
@@ -3601,6 +3628,9 @@
       <c r="P61" t="str">
         <v>Add</v>
       </c>
+      <c r="Q61" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
@@ -3651,6 +3681,9 @@
       <c r="P62" t="str">
         <v>Add</v>
       </c>
+      <c r="Q62" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
@@ -3701,6 +3734,9 @@
       <c r="P63" t="str">
         <v>Add</v>
       </c>
+      <c r="Q63" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
@@ -3751,6 +3787,9 @@
       <c r="P64" t="str">
         <v>Add</v>
       </c>
+      <c r="Q64" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
@@ -3801,6 +3840,9 @@
       <c r="P65" t="str">
         <v>Add</v>
       </c>
+      <c r="Q65" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
@@ -3851,6 +3893,9 @@
       <c r="P66" t="str">
         <v>Add</v>
       </c>
+      <c r="Q66" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
@@ -3901,6 +3946,9 @@
       <c r="P67" t="str">
         <v>Add</v>
       </c>
+      <c r="Q67" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
@@ -3951,6 +3999,9 @@
       <c r="P68" t="str">
         <v>Add</v>
       </c>
+      <c r="Q68" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
@@ -4001,6 +4052,9 @@
       <c r="P69" t="str">
         <v>Add</v>
       </c>
+      <c r="Q69" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
@@ -4051,6 +4105,9 @@
       <c r="P70" t="str">
         <v>Add</v>
       </c>
+      <c r="Q70" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
@@ -4101,6 +4158,9 @@
       <c r="P71" t="str">
         <v>Add</v>
       </c>
+      <c r="Q71" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
@@ -4151,6 +4211,9 @@
       <c r="P72" t="str">
         <v>Add</v>
       </c>
+      <c r="Q72" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
@@ -4201,6 +4264,9 @@
       <c r="P73" t="str">
         <v>Add</v>
       </c>
+      <c r="Q73" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
@@ -4251,6 +4317,9 @@
       <c r="P74" t="str">
         <v>Add</v>
       </c>
+      <c r="Q74" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
@@ -4301,6 +4370,9 @@
       <c r="P75" t="str">
         <v>Add</v>
       </c>
+      <c r="Q75" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
@@ -4351,6 +4423,9 @@
       <c r="P76" t="str">
         <v>Add</v>
       </c>
+      <c r="Q76" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
@@ -4401,6 +4476,9 @@
       <c r="P77" t="str">
         <v>Add</v>
       </c>
+      <c r="Q77" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
@@ -4451,6 +4529,9 @@
       <c r="P78" t="str">
         <v>Add</v>
       </c>
+      <c r="Q78" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
@@ -4501,6 +4582,9 @@
       <c r="P79" t="str">
         <v>Add</v>
       </c>
+      <c r="Q79" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
@@ -4551,6 +4635,9 @@
       <c r="P80" t="str">
         <v>Add</v>
       </c>
+      <c r="Q80" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
@@ -4601,6 +4688,9 @@
       <c r="P81" t="str">
         <v>Add</v>
       </c>
+      <c r="Q81" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
@@ -4651,6 +4741,9 @@
       <c r="P82" t="str">
         <v>Add</v>
       </c>
+      <c r="Q82" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
@@ -4701,6 +4794,9 @@
       <c r="P83" t="str">
         <v>Add</v>
       </c>
+      <c r="Q83" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
@@ -4751,6 +4847,9 @@
       <c r="P84" t="str">
         <v>Add</v>
       </c>
+      <c r="Q84" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
@@ -4801,6 +4900,9 @@
       <c r="P85" t="str">
         <v>Add</v>
       </c>
+      <c r="Q85" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
@@ -4851,6 +4953,9 @@
       <c r="P86" t="str">
         <v>Add</v>
       </c>
+      <c r="Q86" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
@@ -4901,6 +5006,9 @@
       <c r="P87" t="str">
         <v>Add</v>
       </c>
+      <c r="Q87" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
@@ -4951,6 +5059,9 @@
       <c r="P88" t="str">
         <v>Add</v>
       </c>
+      <c r="Q88" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
@@ -5001,6 +5112,9 @@
       <c r="P89" t="str">
         <v>Add</v>
       </c>
+      <c r="Q89" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
@@ -5051,6 +5165,9 @@
       <c r="P90" t="str">
         <v>Add</v>
       </c>
+      <c r="Q90" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
@@ -5101,6 +5218,9 @@
       <c r="P91" t="str">
         <v>Add</v>
       </c>
+      <c r="Q91" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
@@ -5151,6 +5271,9 @@
       <c r="P92" t="str">
         <v>Add</v>
       </c>
+      <c r="Q92" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
@@ -5201,6 +5324,9 @@
       <c r="P93" t="str">
         <v>Add</v>
       </c>
+      <c r="Q93" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
@@ -5251,6 +5377,9 @@
       <c r="P94" t="str">
         <v>Add</v>
       </c>
+      <c r="Q94" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
@@ -5301,6 +5430,9 @@
       <c r="P95" t="str">
         <v>Add</v>
       </c>
+      <c r="Q95" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
@@ -5351,6 +5483,9 @@
       <c r="P96" t="str">
         <v>Add</v>
       </c>
+      <c r="Q96" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
@@ -5401,6 +5536,9 @@
       <c r="P97" t="str">
         <v>Add</v>
       </c>
+      <c r="Q97" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
@@ -5451,6 +5589,9 @@
       <c r="P98" t="str">
         <v>Add</v>
       </c>
+      <c r="Q98" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
@@ -5501,6 +5642,9 @@
       <c r="P99" t="str">
         <v>Add</v>
       </c>
+      <c r="Q99" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
@@ -5551,6 +5695,9 @@
       <c r="P100" t="str">
         <v>Add</v>
       </c>
+      <c r="Q100" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
@@ -5600,6 +5747,9 @@
       </c>
       <c r="P101" t="str">
         <v>Add</v>
+      </c>
+      <c r="Q101" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="102">

--- a/volume/output_manual.xlsx
+++ b/volume/output_manual.xlsx
@@ -5801,6 +5801,9 @@
       <c r="P102" t="str">
         <v>Add</v>
       </c>
+      <c r="Q102" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
@@ -5851,6 +5854,9 @@
       <c r="P103" t="str">
         <v>Add</v>
       </c>
+      <c r="Q103" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
@@ -5901,6 +5907,9 @@
       <c r="P104" t="str">
         <v>Add</v>
       </c>
+      <c r="Q104" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
@@ -5951,6 +5960,9 @@
       <c r="P105" t="str">
         <v>Add</v>
       </c>
+      <c r="Q105" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
@@ -6001,6 +6013,9 @@
       <c r="P106" t="str">
         <v>Add</v>
       </c>
+      <c r="Q106" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
@@ -6051,6 +6066,9 @@
       <c r="P107" t="str">
         <v>Add</v>
       </c>
+      <c r="Q107" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
@@ -6101,6 +6119,9 @@
       <c r="P108" t="str">
         <v>Add</v>
       </c>
+      <c r="Q108" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
@@ -6151,6 +6172,9 @@
       <c r="P109" t="str">
         <v>Add</v>
       </c>
+      <c r="Q109" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
@@ -6201,6 +6225,9 @@
       <c r="P110" t="str">
         <v>Add</v>
       </c>
+      <c r="Q110" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
@@ -6251,6 +6278,9 @@
       <c r="P111" t="str">
         <v>Add</v>
       </c>
+      <c r="Q111" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
@@ -6301,6 +6331,9 @@
       <c r="P112" t="str">
         <v>Add</v>
       </c>
+      <c r="Q112" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
@@ -6351,6 +6384,9 @@
       <c r="P113" t="str">
         <v>Add</v>
       </c>
+      <c r="Q113" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
@@ -6401,6 +6437,9 @@
       <c r="P114" t="str">
         <v>Add</v>
       </c>
+      <c r="Q114" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
@@ -6451,6 +6490,9 @@
       <c r="P115" t="str">
         <v>Add</v>
       </c>
+      <c r="Q115" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
@@ -6501,6 +6543,9 @@
       <c r="P116" t="str">
         <v>Add</v>
       </c>
+      <c r="Q116" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
@@ -6551,6 +6596,9 @@
       <c r="P117" t="str">
         <v>Add</v>
       </c>
+      <c r="Q117" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
@@ -6601,6 +6649,9 @@
       <c r="P118" t="str">
         <v>Add</v>
       </c>
+      <c r="Q118" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
@@ -6651,6 +6702,9 @@
       <c r="P119" t="str">
         <v>Add</v>
       </c>
+      <c r="Q119" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
@@ -6701,6 +6755,9 @@
       <c r="P120" t="str">
         <v>Add</v>
       </c>
+      <c r="Q120" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
@@ -6751,6 +6808,9 @@
       <c r="P121" t="str">
         <v>Add</v>
       </c>
+      <c r="Q121" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
@@ -6801,6 +6861,9 @@
       <c r="P122" t="str">
         <v>Add</v>
       </c>
+      <c r="Q122" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
@@ -6851,6 +6914,9 @@
       <c r="P123" t="str">
         <v>Add</v>
       </c>
+      <c r="Q123" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
@@ -6901,6 +6967,9 @@
       <c r="P124" t="str">
         <v>Add</v>
       </c>
+      <c r="Q124" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
@@ -6951,6 +7020,9 @@
       <c r="P125" t="str">
         <v>Add</v>
       </c>
+      <c r="Q125" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
@@ -7001,6 +7073,9 @@
       <c r="P126" t="str">
         <v>Add</v>
       </c>
+      <c r="Q126" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
@@ -7051,6 +7126,9 @@
       <c r="P127" t="str">
         <v>Add</v>
       </c>
+      <c r="Q127" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
@@ -7101,6 +7179,9 @@
       <c r="P128" t="str">
         <v>Add</v>
       </c>
+      <c r="Q128" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
@@ -7151,6 +7232,9 @@
       <c r="P129" t="str">
         <v>Add</v>
       </c>
+      <c r="Q129" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
@@ -7201,6 +7285,9 @@
       <c r="P130" t="str">
         <v>Add</v>
       </c>
+      <c r="Q130" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
@@ -7251,6 +7338,9 @@
       <c r="P131" t="str">
         <v>Add</v>
       </c>
+      <c r="Q131" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
@@ -7301,6 +7391,9 @@
       <c r="P132" t="str">
         <v>Add</v>
       </c>
+      <c r="Q132" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
@@ -7351,6 +7444,9 @@
       <c r="P133" t="str">
         <v>Add</v>
       </c>
+      <c r="Q133" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
@@ -7401,6 +7497,9 @@
       <c r="P134" t="str">
         <v>Add</v>
       </c>
+      <c r="Q134" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
@@ -7451,6 +7550,9 @@
       <c r="P135" t="str">
         <v>Add</v>
       </c>
+      <c r="Q135" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
@@ -7501,6 +7603,9 @@
       <c r="P136" t="str">
         <v>Add</v>
       </c>
+      <c r="Q136" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
@@ -7551,6 +7656,9 @@
       <c r="P137" t="str">
         <v>Add</v>
       </c>
+      <c r="Q137" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
@@ -7601,6 +7709,9 @@
       <c r="P138" t="str">
         <v>Add</v>
       </c>
+      <c r="Q138" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
@@ -7651,6 +7762,9 @@
       <c r="P139" t="str">
         <v>Add</v>
       </c>
+      <c r="Q139" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
@@ -7701,6 +7815,9 @@
       <c r="P140" t="str">
         <v>Add</v>
       </c>
+      <c r="Q140" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
@@ -7751,6 +7868,9 @@
       <c r="P141" t="str">
         <v>Add</v>
       </c>
+      <c r="Q141" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
@@ -7801,6 +7921,9 @@
       <c r="P142" t="str">
         <v>Add</v>
       </c>
+      <c r="Q142" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
@@ -7851,6 +7974,9 @@
       <c r="P143" t="str">
         <v>Add</v>
       </c>
+      <c r="Q143" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
@@ -7901,6 +8027,9 @@
       <c r="P144" t="str">
         <v>Add</v>
       </c>
+      <c r="Q144" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
@@ -7951,6 +8080,9 @@
       <c r="P145" t="str">
         <v>Add</v>
       </c>
+      <c r="Q145" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
@@ -8001,6 +8133,9 @@
       <c r="P146" t="str">
         <v>Add</v>
       </c>
+      <c r="Q146" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
@@ -8051,6 +8186,9 @@
       <c r="P147" t="str">
         <v>Add</v>
       </c>
+      <c r="Q147" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
@@ -8101,6 +8239,9 @@
       <c r="P148" t="str">
         <v>Add</v>
       </c>
+      <c r="Q148" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
@@ -8151,6 +8292,9 @@
       <c r="P149" t="str">
         <v>Add</v>
       </c>
+      <c r="Q149" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
@@ -8200,6 +8344,9 @@
       </c>
       <c r="P150" t="str">
         <v>Add</v>
+      </c>
+      <c r="Q150" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="151">

--- a/volume/output_manual.xlsx
+++ b/volume/output_manual.xlsx
@@ -8448,6 +8448,9 @@
       <c r="P152" t="str">
         <v>Add</v>
       </c>
+      <c r="Q152" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
@@ -8498,6 +8501,9 @@
       <c r="P153" t="str">
         <v>Add</v>
       </c>
+      <c r="Q153" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
@@ -8548,6 +8554,9 @@
       <c r="P154" t="str">
         <v>Add</v>
       </c>
+      <c r="Q154" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
@@ -8598,6 +8607,9 @@
       <c r="P155" t="str">
         <v>Add</v>
       </c>
+      <c r="Q155" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
@@ -8648,6 +8660,9 @@
       <c r="P156" t="str">
         <v>Add</v>
       </c>
+      <c r="Q156" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
@@ -8698,6 +8713,9 @@
       <c r="P157" t="str">
         <v>Add</v>
       </c>
+      <c r="Q157" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
@@ -8748,6 +8766,9 @@
       <c r="P158" t="str">
         <v>Add</v>
       </c>
+      <c r="Q158" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
@@ -8798,6 +8819,9 @@
       <c r="P159" t="str">
         <v>Add</v>
       </c>
+      <c r="Q159" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
@@ -8848,6 +8872,9 @@
       <c r="P160" t="str">
         <v>Add</v>
       </c>
+      <c r="Q160" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
@@ -8898,6 +8925,9 @@
       <c r="P161" t="str">
         <v>Add</v>
       </c>
+      <c r="Q161" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
@@ -8948,6 +8978,9 @@
       <c r="P162" t="str">
         <v>Add</v>
       </c>
+      <c r="Q162" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
@@ -8998,6 +9031,9 @@
       <c r="P163" t="str">
         <v>Add</v>
       </c>
+      <c r="Q163" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
@@ -9048,6 +9084,9 @@
       <c r="P164" t="str">
         <v>Add</v>
       </c>
+      <c r="Q164" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
@@ -9098,6 +9137,9 @@
       <c r="P165" t="str">
         <v>Add</v>
       </c>
+      <c r="Q165" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
@@ -9148,6 +9190,9 @@
       <c r="P166" t="str">
         <v>Add</v>
       </c>
+      <c r="Q166" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
@@ -9198,6 +9243,9 @@
       <c r="P167" t="str">
         <v>Add</v>
       </c>
+      <c r="Q167" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
@@ -9248,6 +9296,9 @@
       <c r="P168" t="str">
         <v>Add</v>
       </c>
+      <c r="Q168" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
@@ -9298,6 +9349,9 @@
       <c r="P169" t="str">
         <v>Add</v>
       </c>
+      <c r="Q169" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
@@ -9348,6 +9402,9 @@
       <c r="P170" t="str">
         <v>Add</v>
       </c>
+      <c r="Q170" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
@@ -9398,6 +9455,9 @@
       <c r="P171" t="str">
         <v>Add</v>
       </c>
+      <c r="Q171" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
@@ -9448,6 +9508,9 @@
       <c r="P172" t="str">
         <v>Add</v>
       </c>
+      <c r="Q172" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
@@ -9498,6 +9561,9 @@
       <c r="P173" t="str">
         <v>Add</v>
       </c>
+      <c r="Q173" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
@@ -9548,6 +9614,9 @@
       <c r="P174" t="str">
         <v>Add</v>
       </c>
+      <c r="Q174" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
@@ -9598,6 +9667,9 @@
       <c r="P175" t="str">
         <v>Add</v>
       </c>
+      <c r="Q175" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
@@ -9648,6 +9720,9 @@
       <c r="P176" t="str">
         <v>Add</v>
       </c>
+      <c r="Q176" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
@@ -9698,6 +9773,9 @@
       <c r="P177" t="str">
         <v>Add</v>
       </c>
+      <c r="Q177" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
@@ -9748,6 +9826,9 @@
       <c r="P178" t="str">
         <v>Add</v>
       </c>
+      <c r="Q178" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
@@ -9798,6 +9879,9 @@
       <c r="P179" t="str">
         <v>Add</v>
       </c>
+      <c r="Q179" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
@@ -9848,6 +9932,9 @@
       <c r="P180" t="str">
         <v>Add</v>
       </c>
+      <c r="Q180" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
@@ -9898,6 +9985,9 @@
       <c r="P181" t="str">
         <v>Add</v>
       </c>
+      <c r="Q181" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
@@ -9948,6 +10038,9 @@
       <c r="P182" t="str">
         <v>Add</v>
       </c>
+      <c r="Q182" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
@@ -9998,6 +10091,9 @@
       <c r="P183" t="str">
         <v>Add</v>
       </c>
+      <c r="Q183" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
@@ -10048,6 +10144,9 @@
       <c r="P184" t="str">
         <v>Add</v>
       </c>
+      <c r="Q184" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
@@ -10098,6 +10197,9 @@
       <c r="P185" t="str">
         <v>Add</v>
       </c>
+      <c r="Q185" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
@@ -10148,6 +10250,9 @@
       <c r="P186" t="str">
         <v>Add</v>
       </c>
+      <c r="Q186" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
@@ -10198,6 +10303,9 @@
       <c r="P187" t="str">
         <v>Add</v>
       </c>
+      <c r="Q187" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
@@ -10248,6 +10356,9 @@
       <c r="P188" t="str">
         <v>Add</v>
       </c>
+      <c r="Q188" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
@@ -10298,6 +10409,9 @@
       <c r="P189" t="str">
         <v>Add</v>
       </c>
+      <c r="Q189" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
@@ -10348,6 +10462,9 @@
       <c r="P190" t="str">
         <v>Add</v>
       </c>
+      <c r="Q190" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
@@ -10398,6 +10515,9 @@
       <c r="P191" t="str">
         <v>Add</v>
       </c>
+      <c r="Q191" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
@@ -10448,6 +10568,9 @@
       <c r="P192" t="str">
         <v>Add</v>
       </c>
+      <c r="Q192" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
@@ -10498,6 +10621,9 @@
       <c r="P193" t="str">
         <v>Add</v>
       </c>
+      <c r="Q193" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
@@ -10548,6 +10674,9 @@
       <c r="P194" t="str">
         <v>Add</v>
       </c>
+      <c r="Q194" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
@@ -10598,6 +10727,9 @@
       <c r="P195" t="str">
         <v>Add</v>
       </c>
+      <c r="Q195" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
@@ -10648,6 +10780,9 @@
       <c r="P196" t="str">
         <v>Add</v>
       </c>
+      <c r="Q196" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
@@ -10698,6 +10833,9 @@
       <c r="P197" t="str">
         <v>Add</v>
       </c>
+      <c r="Q197" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
@@ -10748,6 +10886,9 @@
       <c r="P198" t="str">
         <v>Add</v>
       </c>
+      <c r="Q198" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
@@ -10798,6 +10939,9 @@
       <c r="P199" t="str">
         <v>Add</v>
       </c>
+      <c r="Q199" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
@@ -10848,6 +10992,9 @@
       <c r="P200" t="str">
         <v>Add</v>
       </c>
+      <c r="Q200" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
@@ -10898,6 +11045,9 @@
       <c r="P201" t="str">
         <v>Add</v>
       </c>
+      <c r="Q201" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
@@ -10948,6 +11098,9 @@
       <c r="P202" t="str">
         <v>Add</v>
       </c>
+      <c r="Q202" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
@@ -10998,6 +11151,9 @@
       <c r="P203" t="str">
         <v>Add</v>
       </c>
+      <c r="Q203" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
@@ -11048,6 +11204,9 @@
       <c r="P204" t="str">
         <v>Add</v>
       </c>
+      <c r="Q204" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
@@ -11098,6 +11257,9 @@
       <c r="P205" t="str">
         <v>Add</v>
       </c>
+      <c r="Q205" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
@@ -11148,6 +11310,9 @@
       <c r="P206" t="str">
         <v>Add</v>
       </c>
+      <c r="Q206" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
@@ -11198,6 +11363,9 @@
       <c r="P207" t="str">
         <v>Add</v>
       </c>
+      <c r="Q207" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
@@ -11248,6 +11416,9 @@
       <c r="P208" t="str">
         <v>Add</v>
       </c>
+      <c r="Q208" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
@@ -11298,6 +11469,9 @@
       <c r="P209" t="str">
         <v>Add</v>
       </c>
+      <c r="Q209" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
@@ -11348,6 +11522,9 @@
       <c r="P210" t="str">
         <v>Add</v>
       </c>
+      <c r="Q210" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="str">
@@ -11398,6 +11575,9 @@
       <c r="P211" t="str">
         <v>Add</v>
       </c>
+      <c r="Q211" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="str">
@@ -11448,6 +11628,9 @@
       <c r="P212" t="str">
         <v>Add</v>
       </c>
+      <c r="Q212" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="str">
@@ -11498,6 +11681,9 @@
       <c r="P213" t="str">
         <v>Add</v>
       </c>
+      <c r="Q213" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="str">
@@ -11548,6 +11734,9 @@
       <c r="P214" t="str">
         <v>Add</v>
       </c>
+      <c r="Q214" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="str">
@@ -11598,6 +11787,9 @@
       <c r="P215" t="str">
         <v>Add</v>
       </c>
+      <c r="Q215" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="str">
@@ -11648,6 +11840,9 @@
       <c r="P216" t="str">
         <v>Add</v>
       </c>
+      <c r="Q216" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="str">
@@ -11698,6 +11893,9 @@
       <c r="P217" t="str">
         <v>Add</v>
       </c>
+      <c r="Q217" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="str">
@@ -11748,6 +11946,9 @@
       <c r="P218" t="str">
         <v>Add</v>
       </c>
+      <c r="Q218" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="str">
@@ -11798,6 +11999,9 @@
       <c r="P219" t="str">
         <v>Add</v>
       </c>
+      <c r="Q219" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="str">
@@ -11848,6 +12052,9 @@
       <c r="P220" t="str">
         <v>Add</v>
       </c>
+      <c r="Q220" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="str">
@@ -11898,6 +12105,9 @@
       <c r="P221" t="str">
         <v>Add</v>
       </c>
+      <c r="Q221" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="str">
@@ -11948,6 +12158,9 @@
       <c r="P222" t="str">
         <v>Add</v>
       </c>
+      <c r="Q222" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="str">
@@ -11998,6 +12211,9 @@
       <c r="P223" t="str">
         <v>Add</v>
       </c>
+      <c r="Q223" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="str">
@@ -12048,6 +12264,9 @@
       <c r="P224" t="str">
         <v>Add</v>
       </c>
+      <c r="Q224" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="str">
@@ -12098,6 +12317,9 @@
       <c r="P225" t="str">
         <v>Add</v>
       </c>
+      <c r="Q225" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
@@ -12148,6 +12370,9 @@
       <c r="P226" t="str">
         <v>Add</v>
       </c>
+      <c r="Q226" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
@@ -12198,6 +12423,9 @@
       <c r="P227" t="str">
         <v>Add</v>
       </c>
+      <c r="Q227" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
@@ -12248,6 +12476,9 @@
       <c r="P228" t="str">
         <v>Add</v>
       </c>
+      <c r="Q228" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
@@ -12298,6 +12529,9 @@
       <c r="P229" t="str">
         <v>Add</v>
       </c>
+      <c r="Q229" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
@@ -12348,6 +12582,9 @@
       <c r="P230" t="str">
         <v>Add</v>
       </c>
+      <c r="Q230" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
@@ -12397,6 +12634,9 @@
       </c>
       <c r="P231" t="str">
         <v>Add</v>
+      </c>
+      <c r="Q231" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="232">

--- a/volume/output_manual.xlsx
+++ b/volume/output_manual.xlsx
@@ -12688,6 +12688,9 @@
       <c r="P232" t="str">
         <v>Add</v>
       </c>
+      <c r="Q232" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
@@ -12738,6 +12741,9 @@
       <c r="P233" t="str">
         <v>Add</v>
       </c>
+      <c r="Q233" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
@@ -12788,6 +12794,9 @@
       <c r="P234" t="str">
         <v>Add</v>
       </c>
+      <c r="Q234" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
@@ -12838,6 +12847,9 @@
       <c r="P235" t="str">
         <v>Add</v>
       </c>
+      <c r="Q235" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
@@ -12888,6 +12900,9 @@
       <c r="P236" t="str">
         <v>Add</v>
       </c>
+      <c r="Q236" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="str">
@@ -12938,6 +12953,9 @@
       <c r="P237" t="str">
         <v>Add</v>
       </c>
+      <c r="Q237" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
@@ -12988,6 +13006,9 @@
       <c r="P238" t="str">
         <v>Add</v>
       </c>
+      <c r="Q238" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="str">
@@ -13038,6 +13059,9 @@
       <c r="P239" t="str">
         <v>Add</v>
       </c>
+      <c r="Q239" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="str">
@@ -13088,6 +13112,9 @@
       <c r="P240" t="str">
         <v>Add</v>
       </c>
+      <c r="Q240" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="str">
@@ -13138,6 +13165,9 @@
       <c r="P241" t="str">
         <v>Add</v>
       </c>
+      <c r="Q241" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="str">
@@ -13188,6 +13218,9 @@
       <c r="P242" t="str">
         <v>Add</v>
       </c>
+      <c r="Q242" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="str">
@@ -13238,6 +13271,9 @@
       <c r="P243" t="str">
         <v>Add</v>
       </c>
+      <c r="Q243" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="str">
@@ -13288,6 +13324,9 @@
       <c r="P244" t="str">
         <v>Add</v>
       </c>
+      <c r="Q244" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="str">
@@ -13338,6 +13377,9 @@
       <c r="P245" t="str">
         <v>Add</v>
       </c>
+      <c r="Q245" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="str">
@@ -13388,6 +13430,9 @@
       <c r="P246" t="str">
         <v>Add</v>
       </c>
+      <c r="Q246" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="str">
@@ -13438,6 +13483,9 @@
       <c r="P247" t="str">
         <v>Add</v>
       </c>
+      <c r="Q247" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="str">
@@ -13488,6 +13536,9 @@
       <c r="P248" t="str">
         <v>Add</v>
       </c>
+      <c r="Q248" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="str">
@@ -13538,6 +13589,9 @@
       <c r="P249" t="str">
         <v>Add</v>
       </c>
+      <c r="Q249" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="str">
@@ -13588,6 +13642,9 @@
       <c r="P250" t="str">
         <v>Add</v>
       </c>
+      <c r="Q250" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="str">
@@ -13638,6 +13695,9 @@
       <c r="P251" t="str">
         <v>Add</v>
       </c>
+      <c r="Q251" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="str">
@@ -13688,6 +13748,9 @@
       <c r="P252" t="str">
         <v>Add</v>
       </c>
+      <c r="Q252" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="str">
@@ -13738,6 +13801,9 @@
       <c r="P253" t="str">
         <v>Add</v>
       </c>
+      <c r="Q253" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="str">
@@ -13788,6 +13854,9 @@
       <c r="P254" t="str">
         <v>Add</v>
       </c>
+      <c r="Q254" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="str">
@@ -13838,6 +13907,9 @@
       <c r="P255" t="str">
         <v>Add</v>
       </c>
+      <c r="Q255" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="str">
@@ -13888,6 +13960,9 @@
       <c r="P256" t="str">
         <v>Add</v>
       </c>
+      <c r="Q256" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="str">
@@ -13938,6 +14013,9 @@
       <c r="P257" t="str">
         <v>Add</v>
       </c>
+      <c r="Q257" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="str">
@@ -13988,6 +14066,9 @@
       <c r="P258" t="str">
         <v>Add</v>
       </c>
+      <c r="Q258" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="str">
@@ -14038,6 +14119,9 @@
       <c r="P259" t="str">
         <v>Add</v>
       </c>
+      <c r="Q259" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="str">
@@ -14088,6 +14172,9 @@
       <c r="P260" t="str">
         <v>Add</v>
       </c>
+      <c r="Q260" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="str">
@@ -14138,6 +14225,9 @@
       <c r="P261" t="str">
         <v>Add</v>
       </c>
+      <c r="Q261" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="str">
@@ -14188,6 +14278,9 @@
       <c r="P262" t="str">
         <v>Add</v>
       </c>
+      <c r="Q262" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="str">
@@ -14238,6 +14331,9 @@
       <c r="P263" t="str">
         <v>Add</v>
       </c>
+      <c r="Q263" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="str">
@@ -14288,6 +14384,9 @@
       <c r="P264" t="str">
         <v>Add</v>
       </c>
+      <c r="Q264" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="str">
@@ -14338,6 +14437,9 @@
       <c r="P265" t="str">
         <v>Add</v>
       </c>
+      <c r="Q265" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="str">
@@ -14388,6 +14490,9 @@
       <c r="P266" t="str">
         <v>Add</v>
       </c>
+      <c r="Q266" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="str">
@@ -14438,6 +14543,9 @@
       <c r="P267" t="str">
         <v>Add</v>
       </c>
+      <c r="Q267" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="str">
@@ -14488,6 +14596,9 @@
       <c r="P268" t="str">
         <v>Add</v>
       </c>
+      <c r="Q268" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="str">
@@ -14538,6 +14649,9 @@
       <c r="P269" t="str">
         <v>Add</v>
       </c>
+      <c r="Q269" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="str">
@@ -14588,6 +14702,9 @@
       <c r="P270" t="str">
         <v>Add</v>
       </c>
+      <c r="Q270" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="str">
@@ -14638,6 +14755,9 @@
       <c r="P271" t="str">
         <v>Add</v>
       </c>
+      <c r="Q271" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="str">
@@ -14688,6 +14808,9 @@
       <c r="P272" t="str">
         <v>Add</v>
       </c>
+      <c r="Q272" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="str">
@@ -14738,6 +14861,9 @@
       <c r="P273" t="str">
         <v>Add</v>
       </c>
+      <c r="Q273" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="str">
@@ -14788,6 +14914,9 @@
       <c r="P274" t="str">
         <v>Add</v>
       </c>
+      <c r="Q274" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="str">
@@ -14838,6 +14967,9 @@
       <c r="P275" t="str">
         <v>Add</v>
       </c>
+      <c r="Q275" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="str">
@@ -14888,6 +15020,9 @@
       <c r="P276" t="str">
         <v>Add</v>
       </c>
+      <c r="Q276" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="str">
@@ -14938,6 +15073,9 @@
       <c r="P277" t="str">
         <v>Add</v>
       </c>
+      <c r="Q277" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="str">
@@ -14988,6 +15126,9 @@
       <c r="P278" t="str">
         <v>Add</v>
       </c>
+      <c r="Q278" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="str">
@@ -15038,6 +15179,9 @@
       <c r="P279" t="str">
         <v>Add</v>
       </c>
+      <c r="Q279" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="str">
@@ -15087,6 +15231,9 @@
       </c>
       <c r="P280" t="str">
         <v>Add</v>
+      </c>
+      <c r="Q280" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="281">

--- a/volume/output_manual.xlsx
+++ b/volume/output_manual.xlsx
@@ -25994,6 +25994,9 @@
       <c r="P483" t="str">
         <v>Add</v>
       </c>
+      <c r="Q483" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="484">
       <c r="A484" t="str">
@@ -26044,6 +26047,9 @@
       <c r="P484" t="str">
         <v>Add</v>
       </c>
+      <c r="Q484" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="485">
       <c r="A485" t="str">
@@ -26094,6 +26100,9 @@
       <c r="P485" t="str">
         <v>Add</v>
       </c>
+      <c r="Q485" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="486">
       <c r="A486" t="str">
@@ -26144,6 +26153,9 @@
       <c r="P486" t="str">
         <v>Add</v>
       </c>
+      <c r="Q486" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="487">
       <c r="A487" t="str">
@@ -26194,6 +26206,9 @@
       <c r="P487" t="str">
         <v>Add</v>
       </c>
+      <c r="Q487" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="488">
       <c r="A488" t="str">
@@ -26244,6 +26259,9 @@
       <c r="P488" t="str">
         <v>Add</v>
       </c>
+      <c r="Q488" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="489">
       <c r="A489" t="str">
@@ -26294,6 +26312,9 @@
       <c r="P489" t="str">
         <v>Add</v>
       </c>
+      <c r="Q489" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="490">
       <c r="A490" t="str">
@@ -26344,6 +26365,9 @@
       <c r="P490" t="str">
         <v>Add</v>
       </c>
+      <c r="Q490" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="491">
       <c r="A491" t="str">
@@ -26394,6 +26418,9 @@
       <c r="P491" t="str">
         <v>Add</v>
       </c>
+      <c r="Q491" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="492">
       <c r="A492" t="str">
@@ -26444,6 +26471,9 @@
       <c r="P492" t="str">
         <v>Add</v>
       </c>
+      <c r="Q492" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="493">
       <c r="A493" t="str">
@@ -26494,6 +26524,9 @@
       <c r="P493" t="str">
         <v>Add</v>
       </c>
+      <c r="Q493" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="494">
       <c r="A494" t="str">
@@ -26544,6 +26577,9 @@
       <c r="P494" t="str">
         <v>Add</v>
       </c>
+      <c r="Q494" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="495">
       <c r="A495" t="str">
@@ -26594,6 +26630,9 @@
       <c r="P495" t="str">
         <v>Add</v>
       </c>
+      <c r="Q495" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="496">
       <c r="A496" t="str">
@@ -26644,6 +26683,9 @@
       <c r="P496" t="str">
         <v>Add</v>
       </c>
+      <c r="Q496" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="497">
       <c r="A497" t="str">
@@ -26694,6 +26736,9 @@
       <c r="P497" t="str">
         <v>Add</v>
       </c>
+      <c r="Q497" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="498">
       <c r="A498" t="str">
@@ -26744,6 +26789,9 @@
       <c r="P498" t="str">
         <v>Add</v>
       </c>
+      <c r="Q498" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="499">
       <c r="A499" t="str">
@@ -26794,6 +26842,9 @@
       <c r="P499" t="str">
         <v>Add</v>
       </c>
+      <c r="Q499" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="500">
       <c r="A500" t="str">
@@ -26844,6 +26895,9 @@
       <c r="P500" t="str">
         <v>Add</v>
       </c>
+      <c r="Q500" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="501">
       <c r="A501" t="str">
@@ -26894,6 +26948,9 @@
       <c r="P501" t="str">
         <v>Add</v>
       </c>
+      <c r="Q501" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="502">
       <c r="A502" t="str">
@@ -26944,6 +27001,9 @@
       <c r="P502" t="str">
         <v>Add</v>
       </c>
+      <c r="Q502" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="503">
       <c r="A503" t="str">
@@ -26994,6 +27054,9 @@
       <c r="P503" t="str">
         <v>Add</v>
       </c>
+      <c r="Q503" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="504">
       <c r="A504" t="str">
@@ -27044,6 +27107,9 @@
       <c r="P504" t="str">
         <v>Add</v>
       </c>
+      <c r="Q504" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="505">
       <c r="A505" t="str">
@@ -27094,6 +27160,9 @@
       <c r="P505" t="str">
         <v>Add</v>
       </c>
+      <c r="Q505" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="506">
       <c r="A506" t="str">
@@ -27144,6 +27213,9 @@
       <c r="P506" t="str">
         <v>Add</v>
       </c>
+      <c r="Q506" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="507">
       <c r="A507" t="str">
@@ -27194,6 +27266,9 @@
       <c r="P507" t="str">
         <v>Add</v>
       </c>
+      <c r="Q507" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="508">
       <c r="A508" t="str">
@@ -27244,6 +27319,9 @@
       <c r="P508" t="str">
         <v>Add</v>
       </c>
+      <c r="Q508" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="509">
       <c r="A509" t="str">
@@ -27294,6 +27372,9 @@
       <c r="P509" t="str">
         <v>Add</v>
       </c>
+      <c r="Q509" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="510">
       <c r="A510" t="str">
@@ -27344,6 +27425,9 @@
       <c r="P510" t="str">
         <v>Add</v>
       </c>
+      <c r="Q510" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="511">
       <c r="A511" t="str">
@@ -27394,6 +27478,9 @@
       <c r="P511" t="str">
         <v>Add</v>
       </c>
+      <c r="Q511" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="512">
       <c r="A512" t="str">
@@ -27444,6 +27531,9 @@
       <c r="P512" t="str">
         <v>Add</v>
       </c>
+      <c r="Q512" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="513">
       <c r="A513" t="str">
@@ -27494,6 +27584,9 @@
       <c r="P513" t="str">
         <v>Add</v>
       </c>
+      <c r="Q513" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="514">
       <c r="A514" t="str">
@@ -27544,6 +27637,9 @@
       <c r="P514" t="str">
         <v>Add</v>
       </c>
+      <c r="Q514" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="515">
       <c r="A515" t="str">
@@ -27594,6 +27690,9 @@
       <c r="P515" t="str">
         <v>Add</v>
       </c>
+      <c r="Q515" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="516">
       <c r="A516" t="str">
@@ -27644,6 +27743,9 @@
       <c r="P516" t="str">
         <v>Add</v>
       </c>
+      <c r="Q516" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="517">
       <c r="A517" t="str">
@@ -27694,6 +27796,9 @@
       <c r="P517" t="str">
         <v>Add</v>
       </c>
+      <c r="Q517" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="518">
       <c r="A518" t="str">
@@ -27744,6 +27849,9 @@
       <c r="P518" t="str">
         <v>Add</v>
       </c>
+      <c r="Q518" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="519">
       <c r="A519" t="str">
@@ -27794,6 +27902,9 @@
       <c r="P519" t="str">
         <v>Add</v>
       </c>
+      <c r="Q519" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="520">
       <c r="A520" t="str">
@@ -27844,6 +27955,9 @@
       <c r="P520" t="str">
         <v>Add</v>
       </c>
+      <c r="Q520" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="521">
       <c r="A521" t="str">
@@ -27894,6 +28008,9 @@
       <c r="P521" t="str">
         <v>Add</v>
       </c>
+      <c r="Q521" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="522">
       <c r="A522" t="str">
@@ -27944,6 +28061,9 @@
       <c r="P522" t="str">
         <v>Add</v>
       </c>
+      <c r="Q522" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="523">
       <c r="A523" t="str">
@@ -27994,6 +28114,9 @@
       <c r="P523" t="str">
         <v>Add</v>
       </c>
+      <c r="Q523" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="524">
       <c r="A524" t="str">
@@ -28044,6 +28167,9 @@
       <c r="P524" t="str">
         <v>Add</v>
       </c>
+      <c r="Q524" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="525">
       <c r="A525" t="str">
@@ -28094,6 +28220,9 @@
       <c r="P525" t="str">
         <v>Add</v>
       </c>
+      <c r="Q525" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="526">
       <c r="A526" t="str">
@@ -28144,6 +28273,9 @@
       <c r="P526" t="str">
         <v>Add</v>
       </c>
+      <c r="Q526" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="527">
       <c r="A527" t="str">
@@ -28194,6 +28326,9 @@
       <c r="P527" t="str">
         <v>Add</v>
       </c>
+      <c r="Q527" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="528">
       <c r="A528" t="str">
@@ -28244,6 +28379,9 @@
       <c r="P528" t="str">
         <v>Add</v>
       </c>
+      <c r="Q528" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="529">
       <c r="A529" t="str">
@@ -28294,6 +28432,9 @@
       <c r="P529" t="str">
         <v>Add</v>
       </c>
+      <c r="Q529" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="530">
       <c r="A530" t="str">
@@ -28344,6 +28485,9 @@
       <c r="P530" t="str">
         <v>Add</v>
       </c>
+      <c r="Q530" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="531">
       <c r="A531" t="str">
@@ -28394,6 +28538,9 @@
       <c r="P531" t="str">
         <v>Add</v>
       </c>
+      <c r="Q531" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="532">
       <c r="A532" t="str">
@@ -28443,6 +28590,9 @@
       </c>
       <c r="P532" t="str">
         <v>Add</v>
+      </c>
+      <c r="Q532" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="533">

--- a/volume/output_manual.xlsx
+++ b/volume/output_manual.xlsx
@@ -28644,6 +28644,9 @@
       <c r="P533" t="str">
         <v>Add</v>
       </c>
+      <c r="Q533" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="534">
       <c r="A534" t="str">
@@ -28694,6 +28697,9 @@
       <c r="P534" t="str">
         <v>Add</v>
       </c>
+      <c r="Q534" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="535">
       <c r="A535" t="str">
@@ -28744,6 +28750,9 @@
       <c r="P535" t="str">
         <v>Add</v>
       </c>
+      <c r="Q535" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="536">
       <c r="A536" t="str">
@@ -28794,6 +28803,9 @@
       <c r="P536" t="str">
         <v>Add</v>
       </c>
+      <c r="Q536" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="537">
       <c r="A537" t="str">
@@ -28844,6 +28856,9 @@
       <c r="P537" t="str">
         <v>Add</v>
       </c>
+      <c r="Q537" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="538">
       <c r="A538" t="str">
@@ -28894,6 +28909,9 @@
       <c r="P538" t="str">
         <v>Add</v>
       </c>
+      <c r="Q538" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="539">
       <c r="A539" t="str">
@@ -28944,6 +28962,9 @@
       <c r="P539" t="str">
         <v>Add</v>
       </c>
+      <c r="Q539" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="540">
       <c r="A540" t="str">
@@ -28994,6 +29015,9 @@
       <c r="P540" t="str">
         <v>Add</v>
       </c>
+      <c r="Q540" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="541">
       <c r="A541" t="str">
@@ -29044,6 +29068,9 @@
       <c r="P541" t="str">
         <v>Add</v>
       </c>
+      <c r="Q541" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="542">
       <c r="A542" t="str">
@@ -29094,6 +29121,9 @@
       <c r="P542" t="str">
         <v>Add</v>
       </c>
+      <c r="Q542" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="543">
       <c r="A543" t="str">
@@ -29144,6 +29174,9 @@
       <c r="P543" t="str">
         <v>Add</v>
       </c>
+      <c r="Q543" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="544">
       <c r="A544" t="str">
@@ -29194,6 +29227,9 @@
       <c r="P544" t="str">
         <v>Add</v>
       </c>
+      <c r="Q544" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="545">
       <c r="A545" t="str">
@@ -29244,6 +29280,9 @@
       <c r="P545" t="str">
         <v>Add</v>
       </c>
+      <c r="Q545" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="546">
       <c r="A546" t="str">
@@ -29294,6 +29333,9 @@
       <c r="P546" t="str">
         <v>Add</v>
       </c>
+      <c r="Q546" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="547">
       <c r="A547" t="str">
@@ -29344,6 +29386,9 @@
       <c r="P547" t="str">
         <v>Add</v>
       </c>
+      <c r="Q547" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="548">
       <c r="A548" t="str">
@@ -29394,6 +29439,9 @@
       <c r="P548" t="str">
         <v>Add</v>
       </c>
+      <c r="Q548" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="549">
       <c r="A549" t="str">
@@ -29444,6 +29492,9 @@
       <c r="P549" t="str">
         <v>Add</v>
       </c>
+      <c r="Q549" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="550">
       <c r="A550" t="str">
@@ -29494,6 +29545,9 @@
       <c r="P550" t="str">
         <v>Add</v>
       </c>
+      <c r="Q550" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="551">
       <c r="A551" t="str">
@@ -29544,6 +29598,9 @@
       <c r="P551" t="str">
         <v>Add</v>
       </c>
+      <c r="Q551" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="552">
       <c r="A552" t="str">
@@ -29594,6 +29651,9 @@
       <c r="P552" t="str">
         <v>Add</v>
       </c>
+      <c r="Q552" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="553">
       <c r="A553" t="str">
@@ -29644,6 +29704,9 @@
       <c r="P553" t="str">
         <v>Add</v>
       </c>
+      <c r="Q553" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="554">
       <c r="A554" t="str">
@@ -29694,6 +29757,9 @@
       <c r="P554" t="str">
         <v>Add</v>
       </c>
+      <c r="Q554" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="555">
       <c r="A555" t="str">
@@ -29744,6 +29810,9 @@
       <c r="P555" t="str">
         <v>Add</v>
       </c>
+      <c r="Q555" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="556">
       <c r="A556" t="str">
@@ -29794,6 +29863,9 @@
       <c r="P556" t="str">
         <v>Add</v>
       </c>
+      <c r="Q556" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="557">
       <c r="A557" t="str">
@@ -29844,6 +29916,9 @@
       <c r="P557" t="str">
         <v>Add</v>
       </c>
+      <c r="Q557" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="558">
       <c r="A558" t="str">
@@ -29894,6 +29969,9 @@
       <c r="P558" t="str">
         <v>Add</v>
       </c>
+      <c r="Q558" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="559">
       <c r="A559" t="str">
@@ -29944,6 +30022,9 @@
       <c r="P559" t="str">
         <v>Add</v>
       </c>
+      <c r="Q559" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="560">
       <c r="A560" t="str">
@@ -29994,6 +30075,9 @@
       <c r="P560" t="str">
         <v>Add</v>
       </c>
+      <c r="Q560" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="561">
       <c r="A561" t="str">
@@ -30044,6 +30128,9 @@
       <c r="P561" t="str">
         <v>Add</v>
       </c>
+      <c r="Q561" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="562">
       <c r="A562" t="str">
@@ -30094,6 +30181,9 @@
       <c r="P562" t="str">
         <v>Add</v>
       </c>
+      <c r="Q562" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="563">
       <c r="A563" t="str">
@@ -30144,6 +30234,9 @@
       <c r="P563" t="str">
         <v>Add</v>
       </c>
+      <c r="Q563" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="564">
       <c r="A564" t="str">
@@ -30194,6 +30287,9 @@
       <c r="P564" t="str">
         <v>Add</v>
       </c>
+      <c r="Q564" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="565">
       <c r="A565" t="str">
@@ -30244,6 +30340,9 @@
       <c r="P565" t="str">
         <v>Add</v>
       </c>
+      <c r="Q565" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="566">
       <c r="A566" t="str">
@@ -30294,6 +30393,9 @@
       <c r="P566" t="str">
         <v>Add</v>
       </c>
+      <c r="Q566" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="567">
       <c r="A567" t="str">
@@ -30344,6 +30446,9 @@
       <c r="P567" t="str">
         <v>Add</v>
       </c>
+      <c r="Q567" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="568">
       <c r="A568" t="str">
@@ -30394,6 +30499,9 @@
       <c r="P568" t="str">
         <v>Add</v>
       </c>
+      <c r="Q568" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="569">
       <c r="A569" t="str">
@@ -30444,6 +30552,9 @@
       <c r="P569" t="str">
         <v>Add</v>
       </c>
+      <c r="Q569" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="570">
       <c r="A570" t="str">
@@ -30494,6 +30605,9 @@
       <c r="P570" t="str">
         <v>Add</v>
       </c>
+      <c r="Q570" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="571">
       <c r="A571" t="str">
@@ -30544,6 +30658,9 @@
       <c r="P571" t="str">
         <v>Add</v>
       </c>
+      <c r="Q571" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="572">
       <c r="A572" t="str">
@@ -30594,6 +30711,9 @@
       <c r="P572" t="str">
         <v>Add</v>
       </c>
+      <c r="Q572" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="573">
       <c r="A573" t="str">
@@ -30644,6 +30764,9 @@
       <c r="P573" t="str">
         <v>Add</v>
       </c>
+      <c r="Q573" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="574">
       <c r="A574" t="str">
@@ -30694,6 +30817,9 @@
       <c r="P574" t="str">
         <v>Add</v>
       </c>
+      <c r="Q574" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="575">
       <c r="A575" t="str">
@@ -30744,6 +30870,9 @@
       <c r="P575" t="str">
         <v>Add</v>
       </c>
+      <c r="Q575" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="576">
       <c r="A576" t="str">
@@ -30794,6 +30923,9 @@
       <c r="P576" t="str">
         <v>Add</v>
       </c>
+      <c r="Q576" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="577">
       <c r="A577" t="str">
@@ -30844,6 +30976,9 @@
       <c r="P577" t="str">
         <v>Add</v>
       </c>
+      <c r="Q577" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="578">
       <c r="A578" t="str">
@@ -30894,6 +31029,9 @@
       <c r="P578" t="str">
         <v>Add</v>
       </c>
+      <c r="Q578" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="579">
       <c r="A579" t="str">
@@ -30944,6 +31082,9 @@
       <c r="P579" t="str">
         <v>Add</v>
       </c>
+      <c r="Q579" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="580">
       <c r="A580" t="str">
@@ -30994,6 +31135,9 @@
       <c r="P580" t="str">
         <v>Add</v>
       </c>
+      <c r="Q580" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="581">
       <c r="A581" t="str">
@@ -31044,6 +31188,9 @@
       <c r="P581" t="str">
         <v>Add</v>
       </c>
+      <c r="Q581" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="582">
       <c r="A582" t="str">
@@ -31093,6 +31240,9 @@
       </c>
       <c r="P582" t="str">
         <v>Add</v>
+      </c>
+      <c r="Q582" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="583">

--- a/volume/output_manual.xlsx
+++ b/volume/output_manual.xlsx
@@ -507,6 +507,9 @@
       <c r="Q2" t="b">
         <v>1</v>
       </c>
+      <c r="R2" t="str">
+        <v>ADNH.AD</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -560,6 +563,9 @@
       <c r="Q3" t="b">
         <v>1</v>
       </c>
+      <c r="R3" t="str">
+        <v>ALPHADATA.AD</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -613,6 +619,9 @@
       <c r="Q4" t="b">
         <v>1</v>
       </c>
+      <c r="R4" t="str">
+        <v>JULPHAR.AD</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
@@ -666,6 +675,9 @@
       <c r="Q5" t="b">
         <v>1</v>
       </c>
+      <c r="R5" t="str">
+        <v>ALEC.DB</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
@@ -719,6 +731,9 @@
       <c r="Q6" t="b">
         <v>1</v>
       </c>
+      <c r="R6" t="str">
+        <v>ERC.DB</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
@@ -772,6 +787,9 @@
       <c r="Q7" t="b">
         <v>1</v>
       </c>
+      <c r="R7" t="str">
+        <v>NCC.DB</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
@@ -825,6 +843,9 @@
       <c r="Q8" t="b">
         <v>1</v>
       </c>
+      <c r="R8" t="str">
+        <v>TABREED.DB</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
@@ -878,6 +899,9 @@
       <c r="Q9" t="b">
         <v>1</v>
       </c>
+      <c r="R9" t="str">
+        <v>SUKOONTAKAFL.DB</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
@@ -931,6 +955,9 @@
       <c r="Q10" t="b">
         <v>1</v>
       </c>
+      <c r="R10" t="str">
+        <v>UPP.DB</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
@@ -984,6 +1011,9 @@
       <c r="Q11" t="b">
         <v>1</v>
       </c>
+      <c r="R11" t="str">
+        <v>DIBS</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
@@ -1090,6 +1120,9 @@
       <c r="Q13" t="b">
         <v>1</v>
       </c>
+      <c r="R13" t="str">
+        <v>ACCL</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
@@ -1143,6 +1176,9 @@
       <c r="Q14" t="b">
         <v>1</v>
       </c>
+      <c r="R14" t="str">
+        <v>ACIW</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
@@ -1196,6 +1232,9 @@
       <c r="Q15" t="b">
         <v>1</v>
       </c>
+      <c r="R15" t="str">
+        <v>ACFN</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
@@ -1249,6 +1288,9 @@
       <c r="Q16" t="b">
         <v>1</v>
       </c>
+      <c r="R16" t="str">
+        <v>ADPT</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
@@ -1408,6 +1450,9 @@
       <c r="Q19" t="b">
         <v>1</v>
       </c>
+      <c r="R19" t="str">
+        <v>AGCC</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
@@ -1461,6 +1506,9 @@
       <c r="Q20" t="b">
         <v>1</v>
       </c>
+      <c r="R20" t="str">
+        <v>AGYS</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
@@ -1514,6 +1562,9 @@
       <c r="Q21" t="b">
         <v>1</v>
       </c>
+      <c r="R21" t="str">
+        <v>ABNB</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
@@ -1567,6 +1618,9 @@
       <c r="Q22" t="b">
         <v>1</v>
       </c>
+      <c r="R22" t="str">
+        <v>AIRO</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
@@ -1620,6 +1674,9 @@
       <c r="Q23" t="b">
         <v>1</v>
       </c>
+      <c r="R23" t="str">
+        <v>YYAI</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
@@ -1673,6 +1730,9 @@
       <c r="Q24" t="b">
         <v>1</v>
       </c>
+      <c r="R24" t="str">
+        <v>ALKT</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
@@ -1726,6 +1786,9 @@
       <c r="Q25" t="b">
         <v>1</v>
       </c>
+      <c r="R25" t="str">
+        <v>ALNY</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
@@ -1779,6 +1842,9 @@
       <c r="Q26" t="b">
         <v>1</v>
       </c>
+      <c r="R26" t="str">
+        <v>ATGL</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
@@ -1832,6 +1898,9 @@
       <c r="Q27" t="b">
         <v>1</v>
       </c>
+      <c r="R27" t="str">
+        <v>ALTS</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
@@ -1885,6 +1954,9 @@
       <c r="Q28" t="b">
         <v>1</v>
       </c>
+      <c r="R28" t="str">
+        <v>AMBR</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
@@ -1938,6 +2010,9 @@
       <c r="Q29" t="b">
         <v>1</v>
       </c>
+      <c r="R29" t="str">
+        <v>AHMA</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
@@ -1991,6 +2066,9 @@
       <c r="Q30" t="b">
         <v>1</v>
       </c>
+      <c r="R30" t="str">
+        <v>ABAT</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
@@ -2044,6 +2122,9 @@
       <c r="Q31" t="b">
         <v>1</v>
       </c>
+      <c r="R31" t="str">
+        <v>ABTC</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
@@ -2097,6 +2178,9 @@
       <c r="Q32" t="b">
         <v>1</v>
       </c>
+      <c r="R32" t="str">
+        <v>APEI</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
@@ -2150,6 +2234,9 @@
       <c r="Q33" t="b">
         <v>1</v>
       </c>
+      <c r="R33" t="str">
+        <v>NNNN</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
@@ -2203,6 +2290,9 @@
       <c r="Q34" t="b">
         <v>1</v>
       </c>
+      <c r="R34" t="str">
+        <v>ARDX</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
@@ -2309,6 +2399,9 @@
       <c r="Q36" t="b">
         <v>1</v>
       </c>
+      <c r="R36" t="str">
+        <v>ARAI</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
@@ -2362,6 +2455,9 @@
       <c r="Q37" t="b">
         <v>1</v>
       </c>
+      <c r="R37" t="str">
+        <v>ARWR</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
@@ -2415,6 +2511,9 @@
       <c r="Q38" t="b">
         <v>1</v>
       </c>
+      <c r="R38" t="str">
+        <v>ASND</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
@@ -2468,6 +2567,9 @@
       <c r="Q39" t="b">
         <v>1</v>
       </c>
+      <c r="R39" t="str">
+        <v>ASTI</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
@@ -2521,6 +2623,9 @@
       <c r="Q40" t="b">
         <v>1</v>
       </c>
+      <c r="R40" t="str">
+        <v>TOPW</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
@@ -2574,6 +2679,9 @@
       <c r="Q41" t="b">
         <v>1</v>
       </c>
+      <c r="R41" t="str">
+        <v>ALAB</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
@@ -2627,6 +2735,9 @@
       <c r="Q42" t="b">
         <v>1</v>
       </c>
+      <c r="R42" t="str">
+        <v>ZBAI</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
@@ -2680,6 +2791,9 @@
       <c r="Q43" t="b">
         <v>1</v>
       </c>
+      <c r="R43" t="str">
+        <v>ATYR</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
@@ -2733,6 +2847,9 @@
       <c r="Q44" t="b">
         <v>1</v>
       </c>
+      <c r="R44" t="str">
+        <v>AGH</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
@@ -2786,6 +2903,9 @@
       <c r="Q45" t="b">
         <v>1</v>
       </c>
+      <c r="R45" t="str">
+        <v>AUPH</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
@@ -2839,6 +2959,9 @@
       <c r="Q46" t="b">
         <v>1</v>
       </c>
+      <c r="R46" t="str">
+        <v>AUPH</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
@@ -2892,6 +3015,9 @@
       <c r="Q47" t="b">
         <v>1</v>
       </c>
+      <c r="R47" t="str">
+        <v>AUID</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
@@ -2945,6 +3071,9 @@
       <c r="Q48" t="b">
         <v>1</v>
       </c>
+      <c r="R48" t="str">
+        <v>ALBT</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
@@ -2998,6 +3127,9 @@
       <c r="Q49" t="b">
         <v>1</v>
       </c>
+      <c r="R49" t="str">
+        <v>AVX</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
@@ -3051,6 +3183,9 @@
       <c r="Q50" t="b">
         <v>1</v>
       </c>
+      <c r="R50" t="str">
+        <v>AVPT</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
@@ -3104,6 +3239,9 @@
       <c r="Q51" t="b">
         <v>1</v>
       </c>
+      <c r="R51" t="str">
+        <v>AVBH</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
@@ -3157,6 +3295,9 @@
       <c r="Q52" t="b">
         <v>1</v>
       </c>
+      <c r="R52" t="str">
+        <v>AWRE</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
@@ -3210,6 +3351,9 @@
       <c r="Q53" t="b">
         <v>1</v>
       </c>
+      <c r="R53" t="str">
+        <v>AZTA</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
@@ -3263,6 +3407,9 @@
       <c r="Q54" t="b">
         <v>1</v>
       </c>
+      <c r="R54" t="str">
+        <v>BDMD</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
@@ -3316,6 +3463,9 @@
       <c r="Q55" t="b">
         <v>1</v>
       </c>
+      <c r="R55" t="str">
+        <v>BMGL</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
@@ -3369,6 +3519,9 @@
       <c r="Q56" t="b">
         <v>1</v>
       </c>
+      <c r="R56" t="str">
+        <v>BLIV</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
@@ -3475,6 +3628,9 @@
       <c r="Q58" t="b">
         <v>1</v>
       </c>
+      <c r="R58" t="str">
+        <v>BKYI</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
@@ -3528,6 +3684,9 @@
       <c r="Q59" t="b">
         <v>1</v>
       </c>
+      <c r="R59" t="str">
+        <v>BNGO</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
@@ -3581,6 +3740,9 @@
       <c r="Q60" t="b">
         <v>1</v>
       </c>
+      <c r="R60" t="str">
+        <v>BNTX</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
@@ -3687,6 +3849,9 @@
       <c r="Q62" t="b">
         <v>1</v>
       </c>
+      <c r="R62" t="str">
+        <v>BRCB</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
@@ -3740,6 +3905,9 @@
       <c r="Q63" t="b">
         <v>1</v>
       </c>
+      <c r="R63" t="str">
+        <v>BNKK</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
@@ -3793,6 +3961,9 @@
       <c r="Q64" t="b">
         <v>1</v>
       </c>
+      <c r="R64" t="str">
+        <v>BRLS</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
@@ -3846,6 +4017,9 @@
       <c r="Q65" t="b">
         <v>1</v>
       </c>
+      <c r="R65" t="str">
+        <v>SLMT</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
@@ -3899,6 +4073,9 @@
       <c r="Q66" t="b">
         <v>1</v>
       </c>
+      <c r="R66" t="str">
+        <v>BUUU</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
@@ -3952,6 +4129,9 @@
       <c r="Q67" t="b">
         <v>1</v>
       </c>
+      <c r="R67" t="str">
+        <v>BVFL</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
@@ -4005,6 +4185,9 @@
       <c r="Q68" t="b">
         <v>1</v>
       </c>
+      <c r="R68" t="str">
+        <v>BCAL</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
@@ -4058,6 +4241,9 @@
       <c r="Q69" t="b">
         <v>1</v>
       </c>
+      <c r="R69" t="str">
+        <v>CV</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
@@ -4111,6 +4297,9 @@
       <c r="Q70" t="b">
         <v>1</v>
       </c>
+      <c r="R70" t="str">
+        <v>CRBU</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
@@ -4164,6 +4353,9 @@
       <c r="Q71" t="b">
         <v>1</v>
       </c>
+      <c r="R71" t="str">
+        <v>CAI</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
@@ -4217,6 +4409,9 @@
       <c r="Q72" t="b">
         <v>1</v>
       </c>
+      <c r="R72" t="str">
+        <v>CASS</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
@@ -4270,6 +4465,9 @@
       <c r="Q73" t="b">
         <v>1</v>
       </c>
+      <c r="R73" t="str">
+        <v>CBFV</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
@@ -4323,6 +4521,9 @@
       <c r="Q74" t="b">
         <v>1</v>
       </c>
+      <c r="R74" t="str">
+        <v>CCHH</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
@@ -4376,6 +4577,9 @@
       <c r="Q75" t="b">
         <v>1</v>
       </c>
+      <c r="R75" t="str">
+        <v>CELU</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
@@ -4429,6 +4633,9 @@
       <c r="Q76" t="b">
         <v>1</v>
       </c>
+      <c r="R76" t="str">
+        <v>CBC</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
@@ -4482,6 +4689,9 @@
       <c r="Q77" t="b">
         <v>1</v>
       </c>
+      <c r="R77" t="str">
+        <v>CHA</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
@@ -4535,6 +4745,9 @@
       <c r="Q78" t="b">
         <v>1</v>
       </c>
+      <c r="R78" t="str">
+        <v>MCTA</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
@@ -4641,6 +4854,9 @@
       <c r="Q80" t="b">
         <v>1</v>
       </c>
+      <c r="R80" t="str">
+        <v>CLIK</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
@@ -4694,6 +4910,9 @@
       <c r="Q81" t="b">
         <v>1</v>
       </c>
+      <c r="R81" t="str">
+        <v>UCFI</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
@@ -4747,6 +4966,9 @@
       <c r="Q82" t="b">
         <v>1</v>
       </c>
+      <c r="R82" t="str">
+        <v>COEP</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
@@ -4800,6 +5022,9 @@
       <c r="Q83" t="b">
         <v>1</v>
       </c>
+      <c r="R83" t="str">
+        <v>CHRS</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
@@ -4853,6 +5078,9 @@
       <c r="Q84" t="b">
         <v>1</v>
       </c>
+      <c r="R84" t="str">
+        <v>CMRC</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
@@ -4906,6 +5134,9 @@
       <c r="Q85" t="b">
         <v>1</v>
       </c>
+      <c r="R85" t="str">
+        <v>CIGL</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
@@ -4959,6 +5190,9 @@
       <c r="Q86" t="b">
         <v>1</v>
       </c>
+      <c r="R86" t="str">
+        <v>CHAI</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
@@ -5012,6 +5246,9 @@
       <c r="Q87" t="b">
         <v>1</v>
       </c>
+      <c r="R87" t="str">
+        <v>CRWV</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
@@ -5065,6 +5302,9 @@
       <c r="Q88" t="b">
         <v>1</v>
       </c>
+      <c r="R88" t="str">
+        <v>CSGP</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
@@ -5118,6 +5358,9 @@
       <c r="Q89" t="b">
         <v>1</v>
       </c>
+      <c r="R89" t="str">
+        <v>COYA</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
@@ -5224,6 +5467,9 @@
       <c r="Q91" t="b">
         <v>1</v>
       </c>
+      <c r="R91" t="str">
+        <v>CRWD</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
@@ -5277,6 +5523,9 @@
       <c r="Q92" t="b">
         <v>1</v>
       </c>
+      <c r="R92" t="str">
+        <v>CTW</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
@@ -5330,6 +5579,9 @@
       <c r="Q93" t="b">
         <v>1</v>
       </c>
+      <c r="R93" t="str">
+        <v>CPIX</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
@@ -5383,6 +5635,9 @@
       <c r="Q94" t="b">
         <v>1</v>
       </c>
+      <c r="R94" t="str">
+        <v>CUPR</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
@@ -5436,6 +5691,9 @@
       <c r="Q95" t="b">
         <v>1</v>
       </c>
+      <c r="R95" t="str">
+        <v>CURI</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
@@ -5489,6 +5747,9 @@
       <c r="Q96" t="b">
         <v>1</v>
       </c>
+      <c r="R96" t="str">
+        <v>CYCN</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
@@ -5542,6 +5803,9 @@
       <c r="Q97" t="b">
         <v>1</v>
       </c>
+      <c r="R97" t="str">
+        <v>DKI</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
@@ -5595,6 +5859,9 @@
       <c r="Q98" t="b">
         <v>1</v>
       </c>
+      <c r="R98" t="str">
+        <v>CDRO</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
@@ -5648,6 +5915,9 @@
       <c r="Q99" t="b">
         <v>1</v>
       </c>
+      <c r="R99" t="str">
+        <v>DXST</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
@@ -5701,6 +5971,9 @@
       <c r="Q100" t="b">
         <v>1</v>
       </c>
+      <c r="R100" t="str">
+        <v>DH</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
@@ -5754,6 +6027,9 @@
       <c r="Q101" t="b">
         <v>1</v>
       </c>
+      <c r="R101" t="str">
+        <v>DLXY</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
@@ -5807,6 +6083,9 @@
       <c r="Q102" t="b">
         <v>1</v>
       </c>
+      <c r="R102" t="str">
+        <v>DGNX</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
@@ -5860,6 +6139,9 @@
       <c r="Q103" t="b">
         <v>1</v>
       </c>
+      <c r="R103" t="str">
+        <v>DOMH</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
@@ -5913,6 +6195,9 @@
       <c r="Q104" t="b">
         <v>1</v>
       </c>
+      <c r="R104" t="str">
+        <v>DDI</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
@@ -5966,6 +6251,9 @@
       <c r="Q105" t="b">
         <v>1</v>
       </c>
+      <c r="R105" t="str">
+        <v>DOYU</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
@@ -6019,6 +6307,9 @@
       <c r="Q106" t="b">
         <v>1</v>
       </c>
+      <c r="R106" t="str">
+        <v>TDIC</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
@@ -6072,6 +6363,9 @@
       <c r="Q107" t="b">
         <v>1</v>
       </c>
+      <c r="R107" t="str">
+        <v>DUOL</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
@@ -6178,6 +6472,9 @@
       <c r="Q109" t="b">
         <v>1</v>
       </c>
+      <c r="R109" t="str">
+        <v>ORBS</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
@@ -6231,6 +6528,9 @@
       <c r="Q110" t="b">
         <v>1</v>
       </c>
+      <c r="R110" t="str">
+        <v>ELWT</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
@@ -6284,6 +6584,9 @@
       <c r="Q111" t="b">
         <v>1</v>
       </c>
+      <c r="R111" t="str">
+        <v>EMPG</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
@@ -6337,6 +6640,9 @@
       <c r="Q112" t="b">
         <v>1</v>
       </c>
+      <c r="R112" t="str">
+        <v>ENGS</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
@@ -6390,6 +6696,9 @@
       <c r="Q113" t="b">
         <v>1</v>
       </c>
+      <c r="R113" t="str">
+        <v>ENPH</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
@@ -6443,6 +6752,9 @@
       <c r="Q114" t="b">
         <v>1</v>
       </c>
+      <c r="R114" t="str">
+        <v>ENSC</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
@@ -6496,6 +6808,9 @@
       <c r="Q115" t="b">
         <v>1</v>
       </c>
+      <c r="R115" t="str">
+        <v>EVTV</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
@@ -6549,6 +6864,9 @@
       <c r="Q116" t="b">
         <v>1</v>
       </c>
+      <c r="R116" t="str">
+        <v>EPSM</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
@@ -6602,6 +6920,9 @@
       <c r="Q117" t="b">
         <v>1</v>
       </c>
+      <c r="R117" t="str">
+        <v>ESGL</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
@@ -6655,6 +6976,9 @@
       <c r="Q118" t="b">
         <v>1</v>
       </c>
+      <c r="R118" t="str">
+        <v>EHGO</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
@@ -6708,6 +7032,9 @@
       <c r="Q119" t="b">
         <v>1</v>
       </c>
+      <c r="R119" t="str">
+        <v>EHLD</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
@@ -6761,6 +7088,9 @@
       <c r="Q120" t="b">
         <v>1</v>
       </c>
+      <c r="R120" t="str">
+        <v>XGN</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
@@ -6814,6 +7144,9 @@
       <c r="Q121" t="b">
         <v>1</v>
       </c>
+      <c r="R121" t="str">
+        <v>EXE</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
@@ -6867,6 +7200,9 @@
       <c r="Q122" t="b">
         <v>1</v>
       </c>
+      <c r="R122" t="str">
+        <v>XPON</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
@@ -6920,6 +7256,9 @@
       <c r="Q123" t="b">
         <v>1</v>
       </c>
+      <c r="R123" t="str">
+        <v>FTRK</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
@@ -6973,6 +7312,9 @@
       <c r="Q124" t="b">
         <v>1</v>
       </c>
+      <c r="R124" t="str">
+        <v>FATN</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
@@ -7026,6 +7368,9 @@
       <c r="Q125" t="b">
         <v>1</v>
       </c>
+      <c r="R125" t="str">
+        <v>FBLA</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
@@ -7079,6 +7424,9 @@
       <c r="Q126" t="b">
         <v>1</v>
       </c>
+      <c r="R126" t="str">
+        <v>FEMY</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
@@ -7132,6 +7480,9 @@
       <c r="Q127" t="b">
         <v>1</v>
       </c>
+      <c r="R127" t="str">
+        <v>FENC</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
@@ -7185,6 +7536,9 @@
       <c r="Q128" t="b">
         <v>1</v>
       </c>
+      <c r="R128" t="str">
+        <v>FIEE</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
@@ -7238,6 +7592,9 @@
       <c r="Q129" t="b">
         <v>1</v>
       </c>
+      <c r="R129" t="str">
+        <v>FDSB</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
@@ -7291,6 +7648,9 @@
       <c r="Q130" t="b">
         <v>1</v>
       </c>
+      <c r="R130" t="str">
+        <v>FLY</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
@@ -7344,6 +7704,9 @@
       <c r="Q131" t="b">
         <v>1</v>
       </c>
+      <c r="R131" t="str">
+        <v>FSUN</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
@@ -7397,6 +7760,9 @@
       <c r="Q132" t="b">
         <v>1</v>
       </c>
+      <c r="R132" t="str">
+        <v>FISV</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
@@ -7450,6 +7816,9 @@
       <c r="Q133" t="b">
         <v>1</v>
       </c>
+      <c r="R133" t="str">
+        <v>FCHL</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
@@ -7503,6 +7872,9 @@
       <c r="Q134" t="b">
         <v>1</v>
       </c>
+      <c r="R134" t="str">
+        <v>FORA</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
@@ -7556,6 +7928,9 @@
       <c r="Q135" t="b">
         <v>1</v>
       </c>
+      <c r="R135" t="str">
+        <v>FOXX</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
@@ -7609,6 +7984,9 @@
       <c r="Q136" t="b">
         <v>1</v>
       </c>
+      <c r="R136" t="str">
+        <v>FRSH</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
@@ -7662,6 +8040,9 @@
       <c r="Q137" t="b">
         <v>1</v>
       </c>
+      <c r="R137" t="str">
+        <v>FCEL</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
@@ -7715,6 +8096,9 @@
       <c r="Q138" t="b">
         <v>1</v>
       </c>
+      <c r="R138" t="str">
+        <v>GAME</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
@@ -7768,6 +8152,9 @@
       <c r="Q139" t="b">
         <v>1</v>
       </c>
+      <c r="R139" t="str">
+        <v>GBFH</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
@@ -7874,6 +8261,9 @@
       <c r="Q141" t="b">
         <v>1</v>
       </c>
+      <c r="R141" t="str">
+        <v>GTLB</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
@@ -7927,6 +8317,9 @@
       <c r="Q142" t="b">
         <v>1</v>
       </c>
+      <c r="R142" t="str">
+        <v>GSAT</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
@@ -7980,6 +8373,9 @@
       <c r="Q143" t="b">
         <v>1</v>
       </c>
+      <c r="R143" t="str">
+        <v>GDHG</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
@@ -8033,6 +8429,9 @@
       <c r="Q144" t="b">
         <v>1</v>
       </c>
+      <c r="R144" t="str">
+        <v>GPRE</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
@@ -8086,6 +8485,9 @@
       <c r="Q145" t="b">
         <v>1</v>
       </c>
+      <c r="R145" t="str">
+        <v>GDYN</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
@@ -8192,6 +8594,9 @@
       <c r="Q147" t="b">
         <v>1</v>
       </c>
+      <c r="R147" t="str">
+        <v>GH</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
@@ -8245,6 +8650,9 @@
       <c r="Q148" t="b">
         <v>1</v>
       </c>
+      <c r="R148" t="str">
+        <v>HXHX</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
@@ -8351,6 +8759,9 @@
       <c r="Q150" t="b">
         <v>1</v>
       </c>
+      <c r="R150" t="str">
+        <v>HTFL</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
@@ -8401,6 +8812,9 @@
       <c r="P151" t="str">
         <v>Add</v>
       </c>
+      <c r="R151" t="str">
+        <v>HMR</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
@@ -8454,6 +8868,9 @@
       <c r="Q152" t="b">
         <v>1</v>
       </c>
+      <c r="R152" t="str">
+        <v>IPST</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
@@ -8507,6 +8924,9 @@
       <c r="Q153" t="b">
         <v>1</v>
       </c>
+      <c r="R153" t="str">
+        <v>HTCO</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
@@ -8560,6 +8980,9 @@
       <c r="Q154" t="b">
         <v>1</v>
       </c>
+      <c r="R154" t="str">
+        <v>HCAI</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
@@ -8613,6 +9036,9 @@
       <c r="Q155" t="b">
         <v>1</v>
       </c>
+      <c r="R155" t="str">
+        <v>HUHU</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
@@ -8666,6 +9092,9 @@
       <c r="Q156" t="b">
         <v>1</v>
       </c>
+      <c r="R156" t="str">
+        <v>HWH</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
@@ -8719,6 +9148,9 @@
       <c r="Q157" t="b">
         <v>1</v>
       </c>
+      <c r="R157" t="str">
+        <v>IMCR</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
@@ -8931,6 +9363,9 @@
       <c r="Q161" t="b">
         <v>1</v>
       </c>
+      <c r="R161" t="str">
+        <v>IPM</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
@@ -8984,6 +9419,9 @@
       <c r="Q162" t="b">
         <v>1</v>
       </c>
+      <c r="R162" t="str">
+        <v>NCT</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
@@ -9037,6 +9475,9 @@
       <c r="Q163" t="b">
         <v>1</v>
       </c>
+      <c r="R163" t="str">
+        <v>IDCC</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
@@ -9090,6 +9531,9 @@
       <c r="Q164" t="b">
         <v>1</v>
       </c>
+      <c r="R164" t="str">
+        <v>TILE</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
@@ -9143,6 +9587,9 @@
       <c r="Q165" t="b">
         <v>1</v>
       </c>
+      <c r="R165" t="str">
+        <v>IMXI</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
@@ -9196,6 +9643,9 @@
       <c r="Q166" t="b">
         <v>1</v>
       </c>
+      <c r="R166" t="str">
+        <v>IVVD</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
@@ -9249,6 +9699,9 @@
       <c r="Q167" t="b">
         <v>1</v>
       </c>
+      <c r="R167" t="str">
+        <v>IOVA</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
@@ -9302,6 +9755,9 @@
       <c r="Q168" t="b">
         <v>1</v>
       </c>
+      <c r="R168" t="str">
+        <v>IQST</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
@@ -9355,6 +9811,9 @@
       <c r="Q169" t="b">
         <v>1</v>
       </c>
+      <c r="R169" t="str">
+        <v>ITRI</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
@@ -9408,6 +9867,9 @@
       <c r="Q170" t="b">
         <v>1</v>
       </c>
+      <c r="R170" t="str">
+        <v>JTAI</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
@@ -9461,6 +9923,9 @@
       <c r="Q171" t="b">
         <v>1</v>
       </c>
+      <c r="R171" t="str">
+        <v>JFB</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
@@ -9514,6 +9979,9 @@
       <c r="Q172" t="b">
         <v>1</v>
       </c>
+      <c r="R172" t="str">
+        <v>JL</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
@@ -9567,6 +10035,9 @@
       <c r="Q173" t="b">
         <v>1</v>
       </c>
+      <c r="R173" t="str">
+        <v>DERM</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
@@ -9620,6 +10091,9 @@
       <c r="Q174" t="b">
         <v>1</v>
       </c>
+      <c r="R174" t="str">
+        <v>YMAT</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
@@ -9673,6 +10147,9 @@
       <c r="Q175" t="b">
         <v>1</v>
       </c>
+      <c r="R175" t="str">
+        <v>JLHL</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
@@ -9726,6 +10203,9 @@
       <c r="Q176" t="b">
         <v>1</v>
       </c>
+      <c r="R176" t="str">
+        <v>JXG</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
@@ -9779,6 +10259,9 @@
       <c r="Q177" t="b">
         <v>1</v>
       </c>
+      <c r="R177" t="str">
+        <v>FMFC</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
@@ -9832,6 +10315,9 @@
       <c r="Q178" t="b">
         <v>1</v>
       </c>
+      <c r="R178" t="str">
+        <v>KELYA</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
@@ -9938,6 +10424,9 @@
       <c r="Q180" t="b">
         <v>1</v>
       </c>
+      <c r="R180" t="str">
+        <v>KE</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
@@ -9991,6 +10480,9 @@
       <c r="Q181" t="b">
         <v>1</v>
       </c>
+      <c r="R181" t="str">
+        <v>KRRO</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
@@ -10044,6 +10536,9 @@
       <c r="Q182" t="b">
         <v>1</v>
       </c>
+      <c r="R182" t="str">
+        <v>KMRK</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
@@ -10097,6 +10592,9 @@
       <c r="Q183" t="b">
         <v>1</v>
       </c>
+      <c r="R183" t="str">
+        <v>FSTR</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
@@ -10150,6 +10648,9 @@
       <c r="Q184" t="b">
         <v>1</v>
       </c>
+      <c r="R184" t="str">
+        <v>LNZA</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
@@ -10203,6 +10704,9 @@
       <c r="Q185" t="b">
         <v>1</v>
       </c>
+      <c r="R185" t="str">
+        <v>LGN</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
@@ -10256,6 +10760,9 @@
       <c r="Q186" t="b">
         <v>1</v>
       </c>
+      <c r="R186" t="str">
+        <v>LFS</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
@@ -10309,6 +10816,9 @@
       <c r="Q187" t="b">
         <v>1</v>
       </c>
+      <c r="R187" t="str">
+        <v>LSE</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
@@ -10362,6 +10872,9 @@
       <c r="Q188" t="b">
         <v>1</v>
       </c>
+      <c r="R188" t="str">
+        <v>LHSW</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
@@ -10415,6 +10928,9 @@
       <c r="Q189" t="b">
         <v>1</v>
       </c>
+      <c r="R189" t="str">
+        <v>LMB</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
@@ -10468,6 +10984,9 @@
       <c r="Q190" t="b">
         <v>1</v>
       </c>
+      <c r="R190" t="str">
+        <v>LGCB</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
@@ -10521,6 +11040,9 @@
       <c r="Q191" t="b">
         <v>1</v>
       </c>
+      <c r="R191" t="str">
+        <v>LHAI</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
@@ -10574,6 +11096,9 @@
       <c r="Q192" t="b">
         <v>1</v>
       </c>
+      <c r="R192" t="str">
+        <v>LQDA</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
@@ -10627,6 +11152,9 @@
       <c r="Q193" t="b">
         <v>1</v>
       </c>
+      <c r="R193" t="str">
+        <v>MDGL</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
@@ -10680,6 +11208,9 @@
       <c r="Q194" t="b">
         <v>1</v>
       </c>
+      <c r="R194" t="str">
+        <v>MGNI</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
@@ -10733,6 +11264,9 @@
       <c r="Q195" t="b">
         <v>1</v>
       </c>
+      <c r="R195" t="str">
+        <v>MAGH</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
@@ -10786,6 +11320,9 @@
       <c r="Q196" t="b">
         <v>1</v>
       </c>
+      <c r="R196" t="str">
+        <v>MSGY</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
@@ -10839,6 +11376,9 @@
       <c r="Q197" t="b">
         <v>1</v>
       </c>
+      <c r="R197" t="str">
+        <v>MGRT</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
@@ -10892,6 +11432,9 @@
       <c r="Q198" t="b">
         <v>0</v>
       </c>
+      <c r="R198" t="str">
+        <v>MRSN</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
@@ -10945,6 +11488,9 @@
       <c r="Q199" t="b">
         <v>1</v>
       </c>
+      <c r="R199" t="str">
+        <v>MFI</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
@@ -11104,6 +11650,9 @@
       <c r="Q202" t="b">
         <v>1</v>
       </c>
+      <c r="R202" t="str">
+        <v>MSGM</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
@@ -11157,6 +11706,9 @@
       <c r="Q203" t="b">
         <v>1</v>
       </c>
+      <c r="R203" t="str">
+        <v>NAVN</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
@@ -11210,6 +11762,9 @@
       <c r="Q204" t="b">
         <v>1</v>
       </c>
+      <c r="R204" t="str">
+        <v>NCNO</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
@@ -11263,6 +11818,9 @@
       <c r="Q205" t="b">
         <v>1</v>
       </c>
+      <c r="R205" t="str">
+        <v>NEON</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
@@ -11316,6 +11874,9 @@
       <c r="Q206" t="b">
         <v>1</v>
       </c>
+      <c r="R206" t="str">
+        <v>NTCL</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
@@ -11369,6 +11930,9 @@
       <c r="Q207" t="b">
         <v>1</v>
       </c>
+      <c r="R207" t="str">
+        <v>NTSK</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
@@ -11422,6 +11986,9 @@
       <c r="Q208" t="b">
         <v>1</v>
       </c>
+      <c r="R208" t="str">
+        <v>NTWK</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
@@ -11475,6 +12042,9 @@
       <c r="Q209" t="b">
         <v>1</v>
       </c>
+      <c r="R209" t="str">
+        <v>NWTG</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
@@ -11528,6 +12098,9 @@
       <c r="Q210" t="b">
         <v>1</v>
       </c>
+      <c r="R210" t="str">
+        <v>NXTT</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="str">
@@ -11581,6 +12154,9 @@
       <c r="Q211" t="b">
         <v>1</v>
       </c>
+      <c r="R211" t="str">
+        <v>NXXT</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="str">
@@ -11634,6 +12210,9 @@
       <c r="Q212" t="b">
         <v>1</v>
       </c>
+      <c r="R212" t="str">
+        <v>NVCR</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="str">
@@ -11687,6 +12266,9 @@
       <c r="Q213" t="b">
         <v>1</v>
       </c>
+      <c r="R213" t="str">
+        <v>OTLY</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="str">
@@ -11740,6 +12322,9 @@
       <c r="Q214" t="b">
         <v>1</v>
       </c>
+      <c r="R214" t="str">
+        <v>OWLS</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="str">
@@ -11793,6 +12378,9 @@
       <c r="Q215" t="b">
         <v>1</v>
       </c>
+      <c r="R215" t="str">
+        <v>SVRN</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="str">
@@ -11846,6 +12434,9 @@
       <c r="Q216" t="b">
         <v>1</v>
       </c>
+      <c r="R216" t="str">
+        <v>OLPX</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="str">
@@ -11899,6 +12490,9 @@
       <c r="Q217" t="b">
         <v>1</v>
       </c>
+      <c r="R217" t="str">
+        <v>OMDA</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="str">
@@ -11952,6 +12546,9 @@
       <c r="Q218" t="b">
         <v>1</v>
       </c>
+      <c r="R218" t="str">
+        <v>OMSE</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="str">
@@ -12005,6 +12602,9 @@
       <c r="Q219" t="b">
         <v>1</v>
       </c>
+      <c r="R219" t="str">
+        <v>YDDL</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="str">
@@ -12058,6 +12658,9 @@
       <c r="Q220" t="b">
         <v>1</v>
       </c>
+      <c r="R220" t="str">
+        <v>OSW</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="str">
@@ -12111,6 +12714,9 @@
       <c r="Q221" t="b">
         <v>1</v>
       </c>
+      <c r="R221" t="str">
+        <v>OPK</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="str">
@@ -12164,6 +12770,9 @@
       <c r="Q222" t="b">
         <v>1</v>
       </c>
+      <c r="R222" t="str">
+        <v>OCC</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="str">
@@ -12217,6 +12826,9 @@
       <c r="Q223" t="b">
         <v>1</v>
       </c>
+      <c r="R223" t="str">
+        <v>IRD</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="str">
@@ -12270,6 +12882,9 @@
       <c r="Q224" t="b">
         <v>1</v>
       </c>
+      <c r="R224" t="str">
+        <v>ORGO</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="str">
@@ -12323,6 +12938,9 @@
       <c r="Q225" t="b">
         <v>1</v>
       </c>
+      <c r="R225" t="str">
+        <v>SEED</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
@@ -12376,6 +12994,9 @@
       <c r="Q226" t="b">
         <v>1</v>
       </c>
+      <c r="R226" t="str">
+        <v>OSIS</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
@@ -12429,6 +13050,9 @@
       <c r="Q227" t="b">
         <v>1</v>
       </c>
+      <c r="R227" t="str">
+        <v>OSRH</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
@@ -12482,6 +13106,9 @@
       <c r="Q228" t="b">
         <v>1</v>
       </c>
+      <c r="R228" t="str">
+        <v>PCAR</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
@@ -12535,6 +13162,9 @@
       <c r="Q229" t="b">
         <v>1</v>
       </c>
+      <c r="R229" t="str">
+        <v>PCRX</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
@@ -12641,6 +13271,9 @@
       <c r="Q231" t="b">
         <v>1</v>
       </c>
+      <c r="R231" t="str">
+        <v>PTRN</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
@@ -12694,6 +13327,9 @@
       <c r="Q232" t="b">
         <v>1</v>
       </c>
+      <c r="R232" t="str">
+        <v>PRSO</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
@@ -12747,6 +13383,9 @@
       <c r="Q233" t="b">
         <v>1</v>
       </c>
+      <c r="R233" t="str">
+        <v>PWP</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
@@ -12800,6 +13439,9 @@
       <c r="Q234" t="b">
         <v>1</v>
       </c>
+      <c r="R234" t="str">
+        <v>PHOE</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
@@ -12906,6 +13548,9 @@
       <c r="Q236" t="b">
         <v>1</v>
       </c>
+      <c r="R236" t="str">
+        <v>PFAI</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="str">
@@ -12959,6 +13604,9 @@
       <c r="Q237" t="b">
         <v>1</v>
       </c>
+      <c r="R237" t="str">
+        <v>PLTS</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
@@ -13012,6 +13660,9 @@
       <c r="Q238" t="b">
         <v>1</v>
       </c>
+      <c r="R238" t="str">
+        <v>PSTV</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="str">
@@ -13065,6 +13716,9 @@
       <c r="Q239" t="b">
         <v>1</v>
       </c>
+      <c r="R239" t="str">
+        <v>PSIX</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="str">
@@ -13118,6 +13772,9 @@
       <c r="Q240" t="b">
         <v>1</v>
       </c>
+      <c r="R240" t="str">
+        <v>PC</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="str">
@@ -13171,6 +13828,9 @@
       <c r="Q241" t="b">
         <v>1</v>
       </c>
+      <c r="R241" t="str">
+        <v>PMEC</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="str">
@@ -13224,6 +13884,9 @@
       <c r="Q242" t="b">
         <v>1</v>
       </c>
+      <c r="R242" t="str">
+        <v>PRCT</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="str">
@@ -13277,6 +13940,9 @@
       <c r="Q243" t="b">
         <v>1</v>
       </c>
+      <c r="R243" t="str">
+        <v>PAL</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="str">
@@ -13330,6 +13996,9 @@
       <c r="Q244" t="b">
         <v>1</v>
       </c>
+      <c r="R244" t="str">
+        <v>PSIG</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="str">
@@ -13383,6 +14052,9 @@
       <c r="Q245" t="b">
         <v>1</v>
       </c>
+      <c r="R245" t="str">
+        <v>LUNG</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="str">
@@ -13436,6 +14108,9 @@
       <c r="Q246" t="b">
         <v>1</v>
       </c>
+      <c r="R246" t="str">
+        <v>PBYI</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="str">
@@ -13489,6 +14164,9 @@
       <c r="Q247" t="b">
         <v>1</v>
       </c>
+      <c r="R247" t="str">
+        <v>QMMM</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="str">
@@ -13542,6 +14220,9 @@
       <c r="Q248" t="b">
         <v>1</v>
       </c>
+      <c r="R248" t="str">
+        <v>QTRX</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="str">
@@ -13595,6 +14276,9 @@
       <c r="Q249" t="b">
         <v>1</v>
       </c>
+      <c r="R249" t="str">
+        <v>RDNT</v>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="str">
@@ -13648,6 +14332,9 @@
       <c r="Q250" t="b">
         <v>1</v>
       </c>
+      <c r="R250" t="str">
+        <v>RPID</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="str">
@@ -13701,6 +14388,9 @@
       <c r="Q251" t="b">
         <v>1</v>
       </c>
+      <c r="R251" t="str">
+        <v>REGN</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="str">
@@ -13754,6 +14444,9 @@
       <c r="Q252" t="b">
         <v>1</v>
       </c>
+      <c r="R252" t="str">
+        <v>RGEN</v>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="str">
@@ -13807,6 +14500,9 @@
       <c r="Q253" t="b">
         <v>1</v>
       </c>
+      <c r="R253" t="str">
+        <v>REFR</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="str">
@@ -13860,6 +14556,9 @@
       <c r="Q254" t="b">
         <v>1</v>
       </c>
+      <c r="R254" t="str">
+        <v>RETO</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="str">
@@ -13913,6 +14612,9 @@
       <c r="Q255" t="b">
         <v>1</v>
       </c>
+      <c r="R255" t="str">
+        <v>RZLV</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="str">
@@ -13966,6 +14668,9 @@
       <c r="Q256" t="b">
         <v>1</v>
       </c>
+      <c r="R256" t="str">
+        <v>ANPA</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="str">
@@ -14019,6 +14724,9 @@
       <c r="Q257" t="b">
         <v>1</v>
       </c>
+      <c r="R257" t="str">
+        <v>RIOT</v>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="str">
@@ -14072,6 +14780,9 @@
       <c r="Q258" t="b">
         <v>1</v>
       </c>
+      <c r="R258" t="str">
+        <v>RIVN</v>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="str">
@@ -14125,6 +14836,9 @@
       <c r="Q259" t="b">
         <v>1</v>
       </c>
+      <c r="R259" t="str">
+        <v>NWTN</v>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="str">
@@ -14231,6 +14945,9 @@
       <c r="Q261" t="b">
         <v>1</v>
       </c>
+      <c r="R261" t="str">
+        <v>RKLB</v>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="str">
@@ -14284,6 +15001,9 @@
       <c r="Q262" t="b">
         <v>1</v>
       </c>
+      <c r="R262" t="str">
+        <v>RMCO</v>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="str">
@@ -14337,6 +15057,9 @@
       <c r="Q263" t="b">
         <v>1</v>
       </c>
+      <c r="R263" t="str">
+        <v>RYET</v>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="str">
@@ -14390,6 +15113,9 @@
       <c r="Q264" t="b">
         <v>1</v>
       </c>
+      <c r="R264" t="str">
+        <v>RYOJ</v>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="str">
@@ -14496,6 +15222,9 @@
       <c r="Q266" t="b">
         <v>1</v>
       </c>
+      <c r="R266" t="str">
+        <v>SAIL</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="str">
@@ -14549,6 +15278,9 @@
       <c r="Q267" t="b">
         <v>1</v>
       </c>
+      <c r="R267" t="str">
+        <v>SNDK</v>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="str">
@@ -14602,6 +15334,9 @@
       <c r="Q268" t="b">
         <v>1</v>
       </c>
+      <c r="R268" t="str">
+        <v>SNWV</v>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="str">
@@ -14708,6 +15443,9 @@
       <c r="Q270" t="b">
         <v>1</v>
       </c>
+      <c r="R270" t="str">
+        <v>SCNX</v>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="str">
@@ -14761,6 +15499,9 @@
       <c r="Q271" t="b">
         <v>1</v>
       </c>
+      <c r="R271" t="str">
+        <v>STX</v>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="str">
@@ -14814,6 +15555,9 @@
       <c r="Q272" t="b">
         <v>1</v>
       </c>
+      <c r="R272" t="str">
+        <v>LEDS</v>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="str">
@@ -14867,6 +15611,9 @@
       <c r="Q273" t="b">
         <v>1</v>
       </c>
+      <c r="R273" t="str">
+        <v>SMTC</v>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="str">
@@ -14920,6 +15667,9 @@
       <c r="Q274" t="b">
         <v>1</v>
       </c>
+      <c r="R274" t="str">
+        <v>SGHT</v>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="str">
@@ -14973,6 +15723,9 @@
       <c r="Q275" t="b">
         <v>1</v>
       </c>
+      <c r="R275" t="str">
+        <v>SVCO</v>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="str">
@@ -15026,6 +15779,9 @@
       <c r="Q276" t="b">
         <v>1</v>
       </c>
+      <c r="R276" t="str">
+        <v>EDTK</v>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="str">
@@ -15079,6 +15835,9 @@
       <c r="Q277" t="b">
         <v>1</v>
       </c>
+      <c r="R277" t="str">
+        <v>PN</v>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="str">
@@ -15132,6 +15891,9 @@
       <c r="Q278" t="b">
         <v>1</v>
       </c>
+      <c r="R278" t="str">
+        <v>SLGB</v>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="str">
@@ -15185,6 +15947,9 @@
       <c r="Q279" t="b">
         <v>1</v>
       </c>
+      <c r="R279" t="str">
+        <v>SMTK</v>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="str">
@@ -15238,6 +16003,9 @@
       <c r="Q280" t="b">
         <v>1</v>
       </c>
+      <c r="R280" t="str">
+        <v>SOHU</v>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="str">
@@ -15291,6 +16059,9 @@
       <c r="Q281" t="b">
         <v>1</v>
       </c>
+      <c r="R281" t="str">
+        <v>HSDT</v>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="str">
@@ -15344,6 +16115,9 @@
       <c r="Q282" t="b">
         <v>1</v>
       </c>
+      <c r="R282" t="str">
+        <v>SLSN</v>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="str">
@@ -15397,6 +16171,9 @@
       <c r="Q283" t="b">
         <v>1</v>
       </c>
+      <c r="R283" t="str">
+        <v>STI</v>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="str">
@@ -15450,6 +16227,9 @@
       <c r="Q284" t="b">
         <v>1</v>
       </c>
+      <c r="R284" t="str">
+        <v>SOLS</v>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="str">
@@ -15503,6 +16283,9 @@
       <c r="Q285" t="b">
         <v>1</v>
       </c>
+      <c r="R285" t="str">
+        <v>SSM</v>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="str">
@@ -15556,6 +16339,9 @@
       <c r="Q286" t="b">
         <v>1</v>
       </c>
+      <c r="R286" t="str">
+        <v>SNOA</v>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="str">
@@ -15609,6 +16395,9 @@
       <c r="Q287" t="b">
         <v>1</v>
       </c>
+      <c r="R287" t="str">
+        <v>SOWG</v>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="str">
@@ -15662,6 +16451,9 @@
       <c r="Q288" t="b">
         <v>1</v>
       </c>
+      <c r="R288" t="str">
+        <v>SPOK</v>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="str">
@@ -15715,6 +16507,9 @@
       <c r="Q289" t="b">
         <v>1</v>
       </c>
+      <c r="R289" t="str">
+        <v>SPT</v>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="str">
@@ -15768,6 +16563,9 @@
       <c r="Q290" t="b">
         <v>1</v>
       </c>
+      <c r="R290" t="str">
+        <v>SSII</v>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="str">
@@ -15874,6 +16672,9 @@
       <c r="Q292" t="b">
         <v>1</v>
       </c>
+      <c r="R292" t="str">
+        <v>GASS</v>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="str">
@@ -15927,6 +16728,9 @@
       <c r="Q293" t="b">
         <v>1</v>
       </c>
+      <c r="R293" t="str">
+        <v>SRTA</v>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="str">
@@ -16086,6 +16890,9 @@
       <c r="Q296" t="b">
         <v>1</v>
       </c>
+      <c r="R296" t="str">
+        <v>SSBI</v>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="str">
@@ -16139,6 +16946,9 @@
       <c r="Q297" t="b">
         <v>1</v>
       </c>
+      <c r="R297" t="str">
+        <v>SURG</v>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="str">
@@ -16192,6 +17002,9 @@
       <c r="Q298" t="b">
         <v>1</v>
       </c>
+      <c r="R298" t="str">
+        <v>TNGX</v>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="str">
@@ -16245,6 +17058,9 @@
       <c r="Q299" t="b">
         <v>1</v>
       </c>
+      <c r="R299" t="str">
+        <v>TWAV</v>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="str">
@@ -16298,6 +17114,9 @@
       <c r="Q300" t="b">
         <v>1</v>
       </c>
+      <c r="R300" t="str">
+        <v>TH</v>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="str">
@@ -16351,6 +17170,9 @@
       <c r="Q301" t="b">
         <v>1</v>
       </c>
+      <c r="R301" t="str">
+        <v>TARS</v>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="str">
@@ -16404,6 +17226,9 @@
       <c r="Q302" t="b">
         <v>1</v>
       </c>
+      <c r="R302" t="str">
+        <v>TTGT</v>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="str">
@@ -16457,6 +17282,9 @@
       <c r="Q303" t="b">
         <v>1</v>
       </c>
+      <c r="R303" t="str">
+        <v>XHLD</v>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="str">
@@ -16510,6 +17338,9 @@
       <c r="Q304" t="b">
         <v>1</v>
       </c>
+      <c r="R304" t="str">
+        <v>TNON</v>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="str">
@@ -16563,6 +17394,9 @@
       <c r="Q305" t="b">
         <v>1</v>
       </c>
+      <c r="R305" t="str">
+        <v>TGHL</v>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="str">
@@ -16616,6 +17450,9 @@
       <c r="Q306" t="b">
         <v>1</v>
       </c>
+      <c r="R306" t="str">
+        <v>OLB</v>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="str">
@@ -16669,6 +17506,9 @@
       <c r="Q307" t="b">
         <v>1</v>
       </c>
+      <c r="R307" t="str">
+        <v>TRI.TO</v>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="str">
@@ -16722,6 +17562,9 @@
       <c r="Q308" t="b">
         <v>1</v>
       </c>
+      <c r="R308" t="str">
+        <v>CIIT</v>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="str">
@@ -16775,6 +17618,9 @@
       <c r="Q309" t="b">
         <v>1</v>
       </c>
+      <c r="R309" t="str">
+        <v>TACT</v>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="str">
@@ -16828,6 +17674,9 @@
       <c r="Q310" t="b">
         <v>1</v>
       </c>
+      <c r="R310" t="str">
+        <v>TVTX</v>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="str">
@@ -16881,6 +17730,9 @@
       <c r="Q311" t="b">
         <v>1</v>
       </c>
+      <c r="R311" t="str">
+        <v>RARE</v>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="str">
@@ -16934,6 +17786,9 @@
       <c r="Q312" t="b">
         <v>1</v>
       </c>
+      <c r="R312" t="str">
+        <v>VELO</v>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="str">
@@ -16987,6 +17842,9 @@
       <c r="Q313" t="b">
         <v>1</v>
       </c>
+      <c r="R313" t="str">
+        <v>VRRM</v>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="str">
@@ -17040,6 +17898,9 @@
       <c r="Q314" t="b">
         <v>1</v>
       </c>
+      <c r="R314" t="str">
+        <v>VSTD</v>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="str">
@@ -17093,6 +17954,9 @@
       <c r="Q315" t="b">
         <v>1</v>
       </c>
+      <c r="R315" t="str">
+        <v>VIOT</v>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="str">
@@ -17146,6 +18010,9 @@
       <c r="Q316" t="b">
         <v>1</v>
       </c>
+      <c r="R316" t="str">
+        <v>VSEC</v>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="str">
@@ -17199,6 +18066,9 @@
       <c r="Q317" t="b">
         <v>1</v>
       </c>
+      <c r="R317" t="str">
+        <v>VSEE</v>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="str">
@@ -17252,6 +18122,9 @@
       <c r="Q318" t="b">
         <v>1</v>
       </c>
+      <c r="R318" t="str">
+        <v>HIND</v>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="str">
@@ -17305,6 +18178,9 @@
       <c r="Q319" t="b">
         <v>1</v>
       </c>
+      <c r="R319" t="str">
+        <v>WFF</v>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="str">
@@ -17358,6 +18234,9 @@
       <c r="Q320" t="b">
         <v>1</v>
       </c>
+      <c r="R320" t="str">
+        <v>WBTN</v>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="str">
@@ -17411,6 +18290,9 @@
       <c r="Q321" t="b">
         <v>1</v>
       </c>
+      <c r="R321" t="str">
+        <v>WETO</v>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="str">
@@ -17464,6 +18346,9 @@
       <c r="Q322" t="b">
         <v>1</v>
       </c>
+      <c r="R322" t="str">
+        <v>WGRX</v>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="str">
@@ -17517,6 +18402,9 @@
       <c r="Q323" t="b">
         <v>1</v>
       </c>
+      <c r="R323" t="str">
+        <v>WDC</v>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="str">
@@ -17570,6 +18458,9 @@
       <c r="Q324" t="b">
         <v>1</v>
       </c>
+      <c r="R324" t="str">
+        <v>WXM</v>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="str">
@@ -17623,6 +18514,9 @@
       <c r="Q325" t="b">
         <v>1</v>
       </c>
+      <c r="R325" t="str">
+        <v>WYFI</v>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="str">
@@ -17676,6 +18570,9 @@
       <c r="Q326" t="b">
         <v>1</v>
       </c>
+      <c r="R326" t="str">
+        <v>WW</v>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="str">
@@ -17729,6 +18626,9 @@
       <c r="Q327" t="b">
         <v>1</v>
       </c>
+      <c r="R327" t="str">
+        <v>XBIO</v>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="str">
@@ -17782,6 +18682,9 @@
       <c r="Q328" t="b">
         <v>1</v>
       </c>
+      <c r="R328" t="str">
+        <v>XWIN</v>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="str">
@@ -17835,6 +18738,9 @@
       <c r="Q329" t="b">
         <v>1</v>
       </c>
+      <c r="R329" t="str">
+        <v>YMT</v>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="str">
@@ -17888,6 +18794,9 @@
       <c r="Q330" t="b">
         <v>1</v>
       </c>
+      <c r="R330" t="str">
+        <v>ZEO</v>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="str">
@@ -17941,6 +18850,9 @@
       <c r="Q331" t="b">
         <v>1</v>
       </c>
+      <c r="R331" t="str">
+        <v>BABA</v>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="str">
@@ -17994,6 +18906,9 @@
       <c r="Q332" t="b">
         <v>1</v>
       </c>
+      <c r="R332" t="str">
+        <v>AMBQ</v>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="str">
@@ -18047,6 +18962,9 @@
       <c r="Q333" t="b">
         <v>1</v>
       </c>
+      <c r="R333" t="str">
+        <v>AMWL</v>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="str">
@@ -18100,6 +19018,9 @@
       <c r="Q334" t="b">
         <v>1</v>
       </c>
+      <c r="R334" t="str">
+        <v>AMRZ.SW</v>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="str">
@@ -18153,6 +19074,9 @@
       <c r="Q335" t="b">
         <v>1</v>
       </c>
+      <c r="R335" t="str">
+        <v>AR</v>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="str">
@@ -18206,6 +19130,9 @@
       <c r="Q336" t="b">
         <v>1</v>
       </c>
+      <c r="R336" t="str">
+        <v>APG</v>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="str">
@@ -18259,6 +19186,9 @@
       <c r="Q337" t="b">
         <v>1</v>
       </c>
+      <c r="R337" t="str">
+        <v>AORT</v>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="str">
@@ -18312,6 +19242,9 @@
       <c r="Q338" t="b">
         <v>1</v>
       </c>
+      <c r="R338" t="str">
+        <v>ATI</v>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="str">
@@ -18365,6 +19298,9 @@
       <c r="Q339" t="b">
         <v>1</v>
       </c>
+      <c r="R339" t="str">
+        <v>AZZ</v>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="str">
@@ -18418,6 +19354,9 @@
       <c r="Q340" t="b">
         <v>1</v>
       </c>
+      <c r="R340" t="str">
+        <v>BDC</v>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="str">
@@ -18471,6 +19410,9 @@
       <c r="Q341" t="b">
         <v>1</v>
       </c>
+      <c r="R341" t="str">
+        <v>BGSF</v>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="str">
@@ -18524,6 +19466,9 @@
       <c r="Q342" t="b">
         <v>1</v>
       </c>
+      <c r="R342" t="str">
+        <v>BBAI</v>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="str">
@@ -18577,6 +19522,9 @@
       <c r="Q343" t="b">
         <v>1</v>
       </c>
+      <c r="R343" t="str">
+        <v>BLSH</v>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="str">
@@ -18630,6 +19578,9 @@
       <c r="Q344" t="b">
         <v>1</v>
       </c>
+      <c r="R344" t="str">
+        <v>CACI</v>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="str">
@@ -18683,6 +19634,9 @@
       <c r="Q345" t="b">
         <v>1</v>
       </c>
+      <c r="R345" t="str">
+        <v>CAH</v>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="str">
@@ -18736,6 +19690,9 @@
       <c r="Q346" t="b">
         <v>1</v>
       </c>
+      <c r="R346" t="str">
+        <v>CVNA</v>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="str">
@@ -18789,6 +19746,9 @@
       <c r="Q347" t="b">
         <v>1</v>
       </c>
+      <c r="R347" t="str">
+        <v>CAVA</v>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="str">
@@ -18842,6 +19802,9 @@
       <c r="Q348" t="b">
         <v>1</v>
       </c>
+      <c r="R348" t="str">
+        <v>CBRE</v>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="str">
@@ -18895,6 +19858,9 @@
       <c r="Q349" t="b">
         <v>1</v>
       </c>
+      <c r="R349" t="str">
+        <v>GIB.A.TO</v>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="str">
@@ -18948,6 +19914,9 @@
       <c r="Q350" t="b">
         <v>1</v>
       </c>
+      <c r="R350" t="str">
+        <v>CBNA</v>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="str">
@@ -19001,6 +19970,9 @@
       <c r="Q351" t="b">
         <v>1</v>
       </c>
+      <c r="R351" t="str">
+        <v>CHGG</v>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="str">
@@ -19107,6 +20079,9 @@
       <c r="Q353" t="b">
         <v>1</v>
       </c>
+      <c r="R353" t="str">
+        <v>CDE</v>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="str">
@@ -19160,6 +20135,9 @@
       <c r="Q354" t="b">
         <v>1</v>
       </c>
+      <c r="R354" t="str">
+        <v>COHR</v>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="str">
@@ -19213,6 +20191,9 @@
       <c r="Q355" t="b">
         <v>1</v>
       </c>
+      <c r="R355" t="str">
+        <v>COUR</v>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="str">
@@ -19372,6 +20353,9 @@
       <c r="Q358" t="b">
         <v>1</v>
       </c>
+      <c r="R358" t="str">
+        <v>DCO</v>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="str">
@@ -19425,6 +20409,9 @@
       <c r="Q359" t="b">
         <v>1</v>
       </c>
+      <c r="R359" t="str">
+        <v>ESI</v>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="str">
@@ -19478,6 +20465,9 @@
       <c r="Q360" t="b">
         <v>1</v>
       </c>
+      <c r="R360" t="str">
+        <v>NRGV</v>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="str">
@@ -19531,6 +20521,9 @@
       <c r="Q361" t="b">
         <v>1</v>
       </c>
+      <c r="R361" t="str">
+        <v>ENS</v>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="str">
@@ -19584,6 +20577,9 @@
       <c r="Q362" t="b">
         <v>1</v>
       </c>
+      <c r="R362" t="str">
+        <v>GWH</v>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="str">
@@ -19637,6 +20633,9 @@
       <c r="Q363" t="b">
         <v>1</v>
       </c>
+      <c r="R363" t="str">
+        <v>FLOC</v>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="str">
@@ -19690,6 +20689,9 @@
       <c r="Q364" t="b">
         <v>1</v>
       </c>
+      <c r="R364" t="str">
+        <v>FNV.TO</v>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="str">
@@ -19743,6 +20745,9 @@
       <c r="Q365" t="b">
         <v>1</v>
       </c>
+      <c r="R365" t="str">
+        <v>FDP</v>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="str">
@@ -19796,6 +20801,9 @@
       <c r="Q366" t="b">
         <v>1</v>
       </c>
+      <c r="R366" t="str">
+        <v>GCTS</v>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="str">
@@ -19849,6 +20857,9 @@
       <c r="Q367" t="b">
         <v>1</v>
       </c>
+      <c r="R367" t="str">
+        <v>GENI</v>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="str">
@@ -19955,6 +20966,9 @@
       <c r="Q369" t="b">
         <v>1</v>
       </c>
+      <c r="R369" t="str">
+        <v>GRND</v>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="str">
@@ -20061,6 +21075,9 @@
       <c r="Q371" t="b">
         <v>1</v>
       </c>
+      <c r="R371" t="str">
+        <v>HAYW</v>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="str">
@@ -20167,6 +21184,9 @@
       <c r="Q373" t="b">
         <v>1</v>
       </c>
+      <c r="R373" t="str">
+        <v>HIMS</v>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="str">
@@ -20220,6 +21240,9 @@
       <c r="Q374" t="b">
         <v>1</v>
       </c>
+      <c r="R374" t="str">
+        <v>HNGE</v>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="str">
@@ -20273,6 +21296,9 @@
       <c r="Q375" t="b">
         <v>1</v>
       </c>
+      <c r="R375" t="str">
+        <v>INR</v>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="str">
@@ -20326,6 +21352,9 @@
       <c r="Q376" t="b">
         <v>1</v>
       </c>
+      <c r="R376" t="str">
+        <v>INGR</v>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="str">
@@ -20379,6 +21408,9 @@
       <c r="Q377" t="b">
         <v>1</v>
       </c>
+      <c r="R377" t="str">
+        <v>IFF</v>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="str">
@@ -20485,6 +21517,9 @@
       <c r="Q379" t="b">
         <v>1</v>
       </c>
+      <c r="R379" t="str">
+        <v>JLL</v>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="str">
@@ -20538,6 +21573,9 @@
       <c r="Q380" t="b">
         <v>1</v>
       </c>
+      <c r="R380" t="str">
+        <v>KRMN</v>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="str">
@@ -20591,6 +21629,9 @@
       <c r="Q381" t="b">
         <v>1</v>
       </c>
+      <c r="R381" t="str">
+        <v>LH</v>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="str">
@@ -20644,6 +21685,9 @@
       <c r="Q382" t="b">
         <v>1</v>
       </c>
+      <c r="R382" t="str">
+        <v>LVWR</v>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="str">
@@ -20697,6 +21741,9 @@
       <c r="Q383" t="b">
         <v>1</v>
       </c>
+      <c r="R383" t="str">
+        <v>MHO</v>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="str">
@@ -20750,6 +21797,9 @@
       <c r="Q384" t="b">
         <v>1</v>
       </c>
+      <c r="R384" t="str">
+        <v>MGY</v>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
@@ -20803,6 +21853,9 @@
       <c r="Q385" t="b">
         <v>1</v>
       </c>
+      <c r="R385" t="str">
+        <v>MANU</v>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
@@ -20856,6 +21909,9 @@
       <c r="Q386" t="b">
         <v>1</v>
       </c>
+      <c r="R386" t="str">
+        <v>MA</v>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="str">
@@ -20909,6 +21965,9 @@
       <c r="Q387" t="b">
         <v>1</v>
       </c>
+      <c r="R387" t="str">
+        <v>MUX</v>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="str">
@@ -20962,6 +22021,9 @@
       <c r="Q388" t="b">
         <v>1</v>
       </c>
+      <c r="R388" t="str">
+        <v>MNTN</v>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="str">
@@ -21015,6 +22077,9 @@
       <c r="Q389" t="b">
         <v>1</v>
       </c>
+      <c r="R389" t="str">
+        <v>MCO</v>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="str">
@@ -21121,6 +22186,9 @@
       <c r="Q391" t="b">
         <v>1</v>
       </c>
+      <c r="R391" t="str">
+        <v>PD</v>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="str">
@@ -21174,6 +22242,9 @@
       <c r="Q392" t="b">
         <v>1</v>
       </c>
+      <c r="R392" t="str">
+        <v>PAR</v>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="str">
@@ -21227,6 +22298,9 @@
       <c r="Q393" t="b">
         <v>1</v>
       </c>
+      <c r="R393" t="str">
+        <v>PAY</v>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="str">
@@ -21280,6 +22354,9 @@
       <c r="Q394" t="b">
         <v>1</v>
       </c>
+      <c r="R394" t="str">
+        <v>PXED</v>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="str">
@@ -21333,6 +22410,9 @@
       <c r="Q395" t="b">
         <v>1</v>
       </c>
+      <c r="R395" t="str">
+        <v>PLNT</v>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="str">
@@ -21386,6 +22466,9 @@
       <c r="Q396" t="b">
         <v>1</v>
       </c>
+      <c r="R396" t="str">
+        <v>PRIM</v>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="str">
@@ -21492,6 +22575,9 @@
       <c r="Q398" t="b">
         <v>1</v>
       </c>
+      <c r="R398" t="str">
+        <v>PRSU</v>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="str">
@@ -21545,6 +22631,9 @@
       <c r="Q399" t="b">
         <v>1</v>
       </c>
+      <c r="R399" t="str">
+        <v>QTWO</v>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="str">
@@ -21598,6 +22687,9 @@
       <c r="Q400" t="b">
         <v>1</v>
       </c>
+      <c r="R400" t="str">
+        <v>Q</v>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="str">
@@ -21651,6 +22743,9 @@
       <c r="Q401" t="b">
         <v>1</v>
       </c>
+      <c r="R401" t="str">
+        <v>RAL</v>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="str">
@@ -21704,6 +22799,9 @@
       <c r="Q402" t="b">
         <v>1</v>
       </c>
+      <c r="R402" t="str">
+        <v>RBA.TO</v>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="str">
@@ -21810,6 +22908,9 @@
       <c r="Q404" t="b">
         <v>1</v>
       </c>
+      <c r="R404" t="str">
+        <v>RBLX</v>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="str">
@@ -21863,6 +22964,9 @@
       <c r="Q405" t="b">
         <v>1</v>
       </c>
+      <c r="R405" t="str">
+        <v>SD</v>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="str">
@@ -21916,6 +23020,9 @@
       <c r="Q406" t="b">
         <v>1</v>
       </c>
+      <c r="R406" t="str">
+        <v>SDRL</v>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="str">
@@ -21969,6 +23076,9 @@
       <c r="Q407" t="b">
         <v>1</v>
       </c>
+      <c r="R407" t="str">
+        <v>SHAK</v>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="str">
@@ -22022,6 +23132,9 @@
       <c r="Q408" t="b">
         <v>1</v>
       </c>
+      <c r="R408" t="str">
+        <v>SI</v>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="str">
@@ -22075,6 +23188,9 @@
       <c r="Q409" t="b">
         <v>1</v>
       </c>
+      <c r="R409" t="str">
+        <v>SNOW</v>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="str">
@@ -22181,6 +23297,9 @@
       <c r="Q411" t="b">
         <v>1</v>
       </c>
+      <c r="R411" t="str">
+        <v>LUV</v>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="str">
@@ -22234,6 +23353,9 @@
       <c r="Q412" t="b">
         <v>1</v>
       </c>
+      <c r="R412" t="str">
+        <v>SPB</v>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="str">
@@ -22287,6 +23409,9 @@
       <c r="Q413" t="b">
         <v>1</v>
       </c>
+      <c r="R413" t="str">
+        <v>SPIR</v>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="str">
@@ -22340,6 +23465,9 @@
       <c r="Q414" t="b">
         <v>1</v>
       </c>
+      <c r="R414" t="str">
+        <v>SARO</v>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="str">
@@ -22446,6 +23574,9 @@
       <c r="Q416" t="b">
         <v>1</v>
       </c>
+      <c r="R416" t="str">
+        <v>TRC</v>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="str">
@@ -22499,6 +23630,9 @@
       <c r="Q417" t="b">
         <v>1</v>
       </c>
+      <c r="R417" t="str">
+        <v>TTAM</v>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="str">
@@ -22552,6 +23686,9 @@
       <c r="Q418" t="b">
         <v>1</v>
       </c>
+      <c r="R418" t="str">
+        <v>TKO</v>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="str">
@@ -22605,6 +23742,9 @@
       <c r="Q419" t="b">
         <v>1</v>
       </c>
+      <c r="R419" t="str">
+        <v>TOST</v>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="str">
@@ -22711,6 +23851,9 @@
       <c r="Q421" t="b">
         <v>1</v>
       </c>
+      <c r="R421" t="str">
+        <v>TG</v>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="str">
@@ -22870,6 +24013,9 @@
       <c r="Q424" t="b">
         <v>1</v>
       </c>
+      <c r="R424" t="str">
+        <v>VEEV</v>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="str">
@@ -22923,6 +24069,9 @@
       <c r="Q425" t="b">
         <v>1</v>
       </c>
+      <c r="R425" t="str">
+        <v>VIA</v>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="str">
@@ -22976,6 +24125,9 @@
       <c r="Q426" t="b">
         <v>1</v>
       </c>
+      <c r="R426" t="str">
+        <v>VIK</v>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="str">
@@ -23029,6 +24181,9 @@
       <c r="Q427" t="b">
         <v>1</v>
       </c>
+      <c r="R427" t="str">
+        <v>V</v>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="str">
@@ -23082,6 +24237,9 @@
       <c r="Q428" t="b">
         <v>1</v>
       </c>
+      <c r="R428" t="str">
+        <v>VOYG</v>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="str">
@@ -23188,6 +24346,9 @@
       <c r="Q430" t="b">
         <v>1</v>
       </c>
+      <c r="R430" t="str">
+        <v>WOLF</v>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="str">
@@ -23294,6 +24455,9 @@
       <c r="Q432" t="b">
         <v>1</v>
       </c>
+      <c r="R432" t="str">
+        <v>WK</v>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="str">
@@ -23347,6 +24511,9 @@
       <c r="Q433" t="b">
         <v>1</v>
       </c>
+      <c r="R433" t="str">
+        <v>XPO</v>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
@@ -23400,6 +24567,9 @@
       <c r="Q434" t="b">
         <v>1</v>
       </c>
+      <c r="R434" t="str">
+        <v>AGIG</v>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
@@ -23453,6 +24623,9 @@
       <c r="Q435" t="b">
         <v>1</v>
       </c>
+      <c r="R435" t="str">
+        <v>BMNR</v>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
@@ -23506,6 +24679,9 @@
       <c r="Q436" t="b">
         <v>1</v>
       </c>
+      <c r="R436" t="str">
+        <v>BQ</v>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
@@ -23559,6 +24735,9 @@
       <c r="Q437" t="b">
         <v>1</v>
       </c>
+      <c r="R437" t="str">
+        <v>YCBD</v>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
@@ -23612,6 +24791,9 @@
       <c r="Q438" t="b">
         <v>1</v>
       </c>
+      <c r="R438" t="str">
+        <v>CHOW</v>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
@@ -23665,6 +24847,9 @@
       <c r="Q439" t="b">
         <v>1</v>
       </c>
+      <c r="R439" t="str">
+        <v>EGG</v>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
@@ -23718,6 +24903,9 @@
       <c r="Q440" t="b">
         <v>1</v>
       </c>
+      <c r="R440" t="str">
+        <v>EONR</v>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
@@ -23771,6 +24959,9 @@
       <c r="Q441" t="b">
         <v>1</v>
       </c>
+      <c r="R441" t="str">
+        <v>EXOD</v>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
@@ -23824,6 +25015,9 @@
       <c r="Q442" t="b">
         <v>1</v>
       </c>
+      <c r="R442" t="str">
+        <v>CITR</v>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
@@ -23930,6 +25124,9 @@
       <c r="Q444" t="b">
         <v>1</v>
       </c>
+      <c r="R444" t="str">
+        <v>ROLR</v>
+      </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
@@ -24036,6 +25233,9 @@
       <c r="Q446" t="b">
         <v>1</v>
       </c>
+      <c r="R446" t="str">
+        <v>IE</v>
+      </c>
     </row>
     <row r="447">
       <c r="A447" t="str">
@@ -24089,6 +25289,9 @@
       <c r="Q447" t="b">
         <v>1</v>
       </c>
+      <c r="R447" t="str">
+        <v>MCRP</v>
+      </c>
     </row>
     <row r="448">
       <c r="A448" t="str">
@@ -24142,6 +25345,9 @@
       <c r="Q448" t="b">
         <v>1</v>
       </c>
+      <c r="R448" t="str">
+        <v>MMA</v>
+      </c>
     </row>
     <row r="449">
       <c r="A449" t="str">
@@ -24195,6 +25401,9 @@
       <c r="Q449" t="b">
         <v>1</v>
       </c>
+      <c r="R449" t="str">
+        <v>NEN</v>
+      </c>
     </row>
     <row r="450">
       <c r="A450" t="str">
@@ -24248,6 +25457,9 @@
       <c r="Q450" t="b">
         <v>1</v>
       </c>
+      <c r="R450" t="str">
+        <v>NGD.TO</v>
+      </c>
     </row>
     <row r="451">
       <c r="A451" t="str">
@@ -24301,6 +25513,9 @@
       <c r="Q451" t="b">
         <v>1</v>
       </c>
+      <c r="R451" t="str">
+        <v>NCL</v>
+      </c>
     </row>
     <row r="452">
       <c r="A452" t="str">
@@ -24354,6 +25569,9 @@
       <c r="Q452" t="b">
         <v>1</v>
       </c>
+      <c r="R452" t="str">
+        <v>NBY</v>
+      </c>
     </row>
     <row r="453">
       <c r="A453" t="str">
@@ -24407,6 +25625,9 @@
       <c r="Q453" t="b">
         <v>1</v>
       </c>
+      <c r="R453" t="str">
+        <v>OBE.TO</v>
+      </c>
     </row>
     <row r="454">
       <c r="A454" t="str">
@@ -24460,6 +25681,9 @@
       <c r="Q454" t="b">
         <v>1</v>
       </c>
+      <c r="R454" t="str">
+        <v>PTN</v>
+      </c>
     </row>
     <row r="455">
       <c r="A455" t="str">
@@ -24513,6 +25737,9 @@
       <c r="Q455" t="b">
         <v>1</v>
       </c>
+      <c r="R455" t="str">
+        <v>PTHS</v>
+      </c>
     </row>
     <row r="456">
       <c r="A456" t="str">
@@ -24566,6 +25793,9 @@
       <c r="Q456" t="b">
         <v>1</v>
       </c>
+      <c r="R456" t="str">
+        <v>PMI</v>
+      </c>
     </row>
     <row r="457">
       <c r="A457" t="str">
@@ -24619,6 +25849,9 @@
       <c r="Q457" t="b">
         <v>1</v>
       </c>
+      <c r="R457" t="str">
+        <v>REED</v>
+      </c>
     </row>
     <row r="458">
       <c r="A458" t="str">
@@ -24672,6 +25905,9 @@
       <c r="Q458" t="b">
         <v>1</v>
       </c>
+      <c r="R458" t="str">
+        <v>TCGL</v>
+      </c>
     </row>
     <row r="459">
       <c r="A459" t="str">
@@ -24725,6 +25961,9 @@
       <c r="Q459" t="b">
         <v>1</v>
       </c>
+      <c r="R459" t="str">
+        <v>TGEN</v>
+      </c>
     </row>
     <row r="460">
       <c r="A460" t="str">
@@ -24778,6 +26017,9 @@
       <c r="Q460" t="b">
         <v>1</v>
       </c>
+      <c r="R460" t="str">
+        <v>MGLD</v>
+      </c>
     </row>
     <row r="461">
       <c r="A461" t="str">
@@ -24831,6 +26073,9 @@
       <c r="Q461" t="b">
         <v>0</v>
       </c>
+      <c r="R461" t="str">
+        <v>UAMY</v>
+      </c>
     </row>
     <row r="462">
       <c r="A462" t="str">
@@ -24884,6 +26129,9 @@
       <c r="Q462" t="b">
         <v>1</v>
       </c>
+      <c r="R462" t="str">
+        <v>UUU</v>
+      </c>
     </row>
     <row r="463">
       <c r="A463" t="str">
@@ -24937,6 +26185,9 @@
       <c r="Q463" t="b">
         <v>1</v>
       </c>
+      <c r="R463" t="str">
+        <v>VNTG</v>
+      </c>
     </row>
     <row r="464">
       <c r="A464" t="str">
@@ -24990,6 +26241,9 @@
       <c r="Q464" t="b">
         <v>1</v>
       </c>
+      <c r="R464" t="str">
+        <v>XTNT</v>
+      </c>
     </row>
     <row r="465">
       <c r="A465" t="str">
@@ -25043,6 +26297,9 @@
       <c r="Q465" t="b">
         <v>1</v>
       </c>
+      <c r="R465" t="str">
+        <v>BAG.L</v>
+      </c>
     </row>
     <row r="466">
       <c r="A466" t="str">
@@ -25096,6 +26353,9 @@
       <c r="Q466" t="b">
         <v>1</v>
       </c>
+      <c r="R466" t="str">
+        <v>AIEA.L</v>
+      </c>
     </row>
     <row r="467">
       <c r="A467" t="str">
@@ -25202,6 +26462,9 @@
       <c r="Q468" t="b">
         <v>1</v>
       </c>
+      <c r="R468" t="str">
+        <v>AMCO.L</v>
+      </c>
     </row>
     <row r="469">
       <c r="A469" t="str">
@@ -25255,6 +26518,9 @@
       <c r="Q469" t="b">
         <v>1</v>
       </c>
+      <c r="R469" t="str">
+        <v>ANG.L</v>
+      </c>
     </row>
     <row r="470">
       <c r="A470" t="str">
@@ -25308,6 +26574,9 @@
       <c r="Q470" t="b">
         <v>1</v>
       </c>
+      <c r="R470" t="str">
+        <v>AOTI.L</v>
+      </c>
     </row>
     <row r="471">
       <c r="A471" t="str">
@@ -25361,6 +26630,9 @@
       <c r="Q471" t="b">
         <v>1</v>
       </c>
+      <c r="R471" t="str">
+        <v>AREC.L</v>
+      </c>
     </row>
     <row r="472">
       <c r="A472" t="str">
@@ -25414,6 +26686,9 @@
       <c r="Q472" t="b">
         <v>1</v>
       </c>
+      <c r="R472" t="str">
+        <v>ATN.L</v>
+      </c>
     </row>
     <row r="473">
       <c r="A473" t="str">
@@ -25467,6 +26742,9 @@
       <c r="Q473" t="b">
         <v>1</v>
       </c>
+      <c r="R473" t="str">
+        <v>BAB.L</v>
+      </c>
     </row>
     <row r="474">
       <c r="A474" t="str">
@@ -25520,6 +26798,9 @@
       <c r="Q474" t="b">
         <v>1</v>
       </c>
+      <c r="R474" t="str">
+        <v>BILN.L</v>
+      </c>
     </row>
     <row r="475">
       <c r="A475" t="str">
@@ -25573,6 +26854,9 @@
       <c r="Q475" t="b">
         <v>1</v>
       </c>
+      <c r="R475" t="str">
+        <v>DEBS.L</v>
+      </c>
     </row>
     <row r="476">
       <c r="A476" t="str">
@@ -25626,6 +26910,9 @@
       <c r="Q476" t="b">
         <v>1</v>
       </c>
+      <c r="R476" t="str">
+        <v>BUC.L</v>
+      </c>
     </row>
     <row r="477">
       <c r="A477" t="str">
@@ -25679,6 +26966,9 @@
       <c r="Q477" t="b">
         <v>1</v>
       </c>
+      <c r="R477" t="str">
+        <v>CASP.L</v>
+      </c>
     </row>
     <row r="478">
       <c r="A478" t="str">
@@ -25838,6 +27128,9 @@
       <c r="Q480" t="b">
         <v>1</v>
       </c>
+      <c r="R480" t="str">
+        <v>CREO.L</v>
+      </c>
     </row>
     <row r="481">
       <c r="A481" t="str">
@@ -25891,6 +27184,9 @@
       <c r="Q481" t="b">
         <v>1</v>
       </c>
+      <c r="R481" t="str">
+        <v>TIDE.L</v>
+      </c>
     </row>
     <row r="482">
       <c r="A482" t="str">
@@ -25944,6 +27240,9 @@
       <c r="Q482" t="b">
         <v>1</v>
       </c>
+      <c r="R482" t="str">
+        <v>CSSG.L</v>
+      </c>
     </row>
     <row r="483">
       <c r="A483" t="str">
@@ -25997,6 +27296,9 @@
       <c r="Q483" t="b">
         <v>1</v>
       </c>
+      <c r="R483" t="str">
+        <v>EARN.L</v>
+      </c>
     </row>
     <row r="484">
       <c r="A484" t="str">
@@ -26050,6 +27352,9 @@
       <c r="Q484" t="b">
         <v>1</v>
       </c>
+      <c r="R484" t="str">
+        <v>EAAS.L</v>
+      </c>
     </row>
     <row r="485">
       <c r="A485" t="str">
@@ -26103,6 +27408,9 @@
       <c r="Q485" t="b">
         <v>1</v>
       </c>
+      <c r="R485" t="str">
+        <v>ELCO.L</v>
+      </c>
     </row>
     <row r="486">
       <c r="A486" t="str">
@@ -26156,6 +27464,9 @@
       <c r="Q486" t="b">
         <v>1</v>
       </c>
+      <c r="R486" t="str">
+        <v>ENSI.L</v>
+      </c>
     </row>
     <row r="487">
       <c r="A487" t="str">
@@ -26209,6 +27520,9 @@
       <c r="Q487" t="b">
         <v>1</v>
       </c>
+      <c r="R487" t="str">
+        <v>FIL.L</v>
+      </c>
     </row>
     <row r="488">
       <c r="A488" t="str">
@@ -26262,6 +27576,9 @@
       <c r="Q488" t="b">
         <v>1</v>
       </c>
+      <c r="R488" t="str">
+        <v>FEVR.L</v>
+      </c>
     </row>
     <row r="489">
       <c r="A489" t="str">
@@ -26315,6 +27632,9 @@
       <c r="Q489" t="b">
         <v>1</v>
       </c>
+      <c r="R489" t="str">
+        <v>FGP.L</v>
+      </c>
     </row>
     <row r="490">
       <c r="A490" t="str">
@@ -26421,6 +27741,9 @@
       <c r="Q491" t="b">
         <v>1</v>
       </c>
+      <c r="R491" t="str">
+        <v>GENI.L</v>
+      </c>
     </row>
     <row r="492">
       <c r="A492" t="str">
@@ -26474,6 +27797,9 @@
       <c r="Q492" t="b">
         <v>1</v>
       </c>
+      <c r="R492" t="str">
+        <v>GETB.L</v>
+      </c>
     </row>
     <row r="493">
       <c r="A493" t="str">
@@ -26527,6 +27853,9 @@
       <c r="Q493" t="b">
         <v>1</v>
       </c>
+      <c r="R493" t="str">
+        <v>GST.L</v>
+      </c>
     </row>
     <row r="494">
       <c r="A494" t="str">
@@ -26580,6 +27909,9 @@
       <c r="Q494" t="b">
         <v>1</v>
       </c>
+      <c r="R494" t="str">
+        <v>HDD.L</v>
+      </c>
     </row>
     <row r="495">
       <c r="A495" t="str">
@@ -26633,6 +27965,9 @@
       <c r="Q495" t="b">
         <v>1</v>
       </c>
+      <c r="R495" t="str">
+        <v>HERC.L</v>
+      </c>
     </row>
     <row r="496">
       <c r="A496" t="str">
@@ -26686,6 +28021,9 @@
       <c r="Q496" t="b">
         <v>1</v>
       </c>
+      <c r="R496" t="str">
+        <v>HOC.L</v>
+      </c>
     </row>
     <row r="497">
       <c r="A497" t="str">
@@ -26739,6 +28077,9 @@
       <c r="Q497" t="b">
         <v>1</v>
       </c>
+      <c r="R497" t="str">
+        <v>HWDN.L</v>
+      </c>
     </row>
     <row r="498">
       <c r="A498" t="str">
@@ -26792,6 +28133,9 @@
       <c r="Q498" t="b">
         <v>1</v>
       </c>
+      <c r="R498" t="str">
+        <v>HUD.L</v>
+      </c>
     </row>
     <row r="499">
       <c r="A499" t="str">
@@ -26845,6 +28189,9 @@
       <c r="Q499" t="b">
         <v>1</v>
       </c>
+      <c r="R499" t="str">
+        <v>IGR.L</v>
+      </c>
     </row>
     <row r="500">
       <c r="A500" t="str">
@@ -26898,6 +28245,9 @@
       <c r="Q500" t="b">
         <v>1</v>
       </c>
+      <c r="R500" t="str">
+        <v>IXI.L</v>
+      </c>
     </row>
     <row r="501">
       <c r="A501" t="str">
@@ -26951,6 +28301,9 @@
       <c r="Q501" t="b">
         <v>1</v>
       </c>
+      <c r="R501" t="str">
+        <v>KLR.L</v>
+      </c>
     </row>
     <row r="502">
       <c r="A502" t="str">
@@ -27057,6 +28410,9 @@
       <c r="Q503" t="b">
         <v>1</v>
       </c>
+      <c r="R503" t="str">
+        <v>BTC.L</v>
+      </c>
     </row>
     <row r="504">
       <c r="A504" t="str">
@@ -27110,6 +28466,9 @@
       <c r="Q504" t="b">
         <v>1</v>
       </c>
+      <c r="R504" t="str">
+        <v>LPA.L</v>
+      </c>
     </row>
     <row r="505">
       <c r="A505" t="str">
@@ -27163,6 +28522,9 @@
       <c r="Q505" t="b">
         <v>1</v>
       </c>
+      <c r="R505" t="str">
+        <v>MEGP.L</v>
+      </c>
     </row>
     <row r="506">
       <c r="A506" t="str">
@@ -27216,6 +28578,9 @@
       <c r="Q506" t="b">
         <v>1</v>
       </c>
+      <c r="R506" t="str">
+        <v>MTL.L</v>
+      </c>
     </row>
     <row r="507">
       <c r="A507" t="str">
@@ -27269,6 +28634,9 @@
       <c r="Q507" t="b">
         <v>1</v>
       </c>
+      <c r="R507" t="str">
+        <v>MTC.L</v>
+      </c>
     </row>
     <row r="508">
       <c r="A508" t="str">
@@ -27322,6 +28690,9 @@
       <c r="Q508" t="b">
         <v>1</v>
       </c>
+      <c r="R508" t="str">
+        <v>NCC.L</v>
+      </c>
     </row>
     <row r="509">
       <c r="A509" t="str">
@@ -27375,6 +28746,9 @@
       <c r="Q509" t="b">
         <v>1</v>
       </c>
+      <c r="R509" t="str">
+        <v>NXQ.L</v>
+      </c>
     </row>
     <row r="510">
       <c r="A510" t="str">
@@ -27428,6 +28802,9 @@
       <c r="Q510" t="b">
         <v>1</v>
       </c>
+      <c r="R510" t="str">
+        <v>NEXS.L</v>
+      </c>
     </row>
     <row r="511">
       <c r="A511" t="str">
@@ -27481,6 +28858,9 @@
       <c r="Q511" t="b">
         <v>1</v>
       </c>
+      <c r="R511" t="str">
+        <v>NXR.L</v>
+      </c>
     </row>
     <row r="512">
       <c r="A512" t="str">
@@ -27534,6 +28914,9 @@
       <c r="Q512" t="b">
         <v>1</v>
       </c>
+      <c r="R512" t="str">
+        <v>NBB.L</v>
+      </c>
     </row>
     <row r="513">
       <c r="A513" t="str">
@@ -27587,6 +28970,9 @@
       <c r="Q513" t="b">
         <v>1</v>
       </c>
+      <c r="R513" t="str">
+        <v>OBI.L</v>
+      </c>
     </row>
     <row r="514">
       <c r="A514" t="str">
@@ -27640,6 +29026,9 @@
       <c r="Q514" t="b">
         <v>1</v>
       </c>
+      <c r="R514" t="str">
+        <v>OHGR.AQ</v>
+      </c>
     </row>
     <row r="515">
       <c r="A515" t="str">
@@ -27693,6 +29082,9 @@
       <c r="Q515" t="b">
         <v>0</v>
       </c>
+      <c r="R515" t="str">
+        <v>OPG.L</v>
+      </c>
     </row>
     <row r="516">
       <c r="A516" t="str">
@@ -27746,6 +29138,9 @@
       <c r="Q516" t="b">
         <v>1</v>
       </c>
+      <c r="R516" t="str">
+        <v>OXB.L</v>
+      </c>
     </row>
     <row r="517">
       <c r="A517" t="str">
@@ -27799,6 +29194,9 @@
       <c r="Q517" t="b">
         <v>1</v>
       </c>
+      <c r="R517" t="str">
+        <v>PAY.L</v>
+      </c>
     </row>
     <row r="518">
       <c r="A518" t="str">
@@ -27852,6 +29250,9 @@
       <c r="Q518" t="b">
         <v>1</v>
       </c>
+      <c r="R518" t="str">
+        <v>POW.L</v>
+      </c>
     </row>
     <row r="519">
       <c r="A519" t="str">
@@ -27905,6 +29306,9 @@
       <c r="Q519" t="b">
         <v>1</v>
       </c>
+      <c r="R519" t="str">
+        <v>PPHC.L</v>
+      </c>
     </row>
     <row r="520">
       <c r="A520" t="str">
@@ -27958,6 +29362,9 @@
       <c r="Q520" t="b">
         <v>1</v>
       </c>
+      <c r="R520" t="str">
+        <v>PULS.L</v>
+      </c>
     </row>
     <row r="521">
       <c r="A521" t="str">
@@ -28011,6 +29418,9 @@
       <c r="Q521" t="b">
         <v>1</v>
       </c>
+      <c r="R521" t="str">
+        <v>RPI.L</v>
+      </c>
     </row>
     <row r="522">
       <c r="A522" t="str">
@@ -28117,6 +29527,9 @@
       <c r="Q523" t="b">
         <v>1</v>
       </c>
+      <c r="R523" t="str">
+        <v>RGG.AQ</v>
+      </c>
     </row>
     <row r="524">
       <c r="A524" t="str">
@@ -28170,6 +29583,9 @@
       <c r="Q524" t="b">
         <v>1</v>
       </c>
+      <c r="R524" t="str">
+        <v>RTO.L</v>
+      </c>
     </row>
     <row r="525">
       <c r="A525" t="str">
@@ -28223,6 +29639,9 @@
       <c r="Q525" t="b">
         <v>1</v>
       </c>
+      <c r="R525" t="str">
+        <v>RBN.L</v>
+      </c>
     </row>
     <row r="526">
       <c r="A526" t="str">
@@ -28276,6 +29695,9 @@
       <c r="Q526" t="b">
         <v>1</v>
       </c>
+      <c r="R526" t="str">
+        <v>SEEN.L</v>
+      </c>
     </row>
     <row r="527">
       <c r="A527" t="str">
@@ -28329,6 +29751,9 @@
       <c r="Q527" t="b">
         <v>1</v>
       </c>
+      <c r="R527" t="str">
+        <v>SOS.L</v>
+      </c>
     </row>
     <row r="528">
       <c r="A528" t="str">
@@ -28382,6 +29807,9 @@
       <c r="Q528" t="b">
         <v>1</v>
       </c>
+      <c r="R528" t="str">
+        <v>SPSY.L</v>
+      </c>
     </row>
     <row r="529">
       <c r="A529" t="str">
@@ -28435,6 +29863,9 @@
       <c r="Q529" t="b">
         <v>1</v>
       </c>
+      <c r="R529" t="str">
+        <v>SPR.L</v>
+      </c>
     </row>
     <row r="530">
       <c r="A530" t="str">
@@ -28488,6 +29919,9 @@
       <c r="Q530" t="b">
         <v>1</v>
       </c>
+      <c r="R530" t="str">
+        <v>STEM.L</v>
+      </c>
     </row>
     <row r="531">
       <c r="A531" t="str">
@@ -28541,6 +29975,9 @@
       <c r="Q531" t="b">
         <v>1</v>
       </c>
+      <c r="R531" t="str">
+        <v>SYM.L</v>
+      </c>
     </row>
     <row r="532">
       <c r="A532" t="str">
@@ -28594,6 +30031,9 @@
       <c r="Q532" t="b">
         <v>1</v>
       </c>
+      <c r="R532" t="str">
+        <v>SNX.L</v>
+      </c>
     </row>
     <row r="533">
       <c r="A533" t="str">
@@ -28647,6 +30087,9 @@
       <c r="Q533" t="b">
         <v>1</v>
       </c>
+      <c r="R533" t="str">
+        <v>SYS.L</v>
+      </c>
     </row>
     <row r="534">
       <c r="A534" t="str">
@@ -28700,6 +30143,9 @@
       <c r="Q534" t="b">
         <v>1</v>
       </c>
+      <c r="R534" t="str">
+        <v>TENG.L</v>
+      </c>
     </row>
     <row r="535">
       <c r="A535" t="str">
@@ -28753,6 +30199,9 @@
       <c r="Q535" t="b">
         <v>1</v>
       </c>
+      <c r="R535" t="str">
+        <v>TIA.L</v>
+      </c>
     </row>
     <row r="536">
       <c r="A536" t="str">
@@ -28806,6 +30255,9 @@
       <c r="Q536" t="b">
         <v>1</v>
       </c>
+      <c r="R536" t="str">
+        <v>TIME.L</v>
+      </c>
     </row>
     <row r="537">
       <c r="A537" t="str">
@@ -28859,6 +30311,9 @@
       <c r="Q537" t="b">
         <v>1</v>
       </c>
+      <c r="R537" t="str">
+        <v>TBLD.L</v>
+      </c>
     </row>
     <row r="538">
       <c r="A538" t="str">
@@ -28912,6 +30367,9 @@
       <c r="Q538" t="b">
         <v>1</v>
       </c>
+      <c r="R538" t="str">
+        <v>VNET.L</v>
+      </c>
     </row>
     <row r="539">
       <c r="A539" t="str">
@@ -28965,6 +30423,9 @@
       <c r="Q539" t="b">
         <v>1</v>
       </c>
+      <c r="R539" t="str">
+        <v>WIX.L</v>
+      </c>
     </row>
     <row r="540">
       <c r="A540" t="str">
@@ -29018,6 +30479,9 @@
       <c r="Q540" t="b">
         <v>1</v>
       </c>
+      <c r="R540" t="str">
+        <v>WYN.L</v>
+      </c>
     </row>
     <row r="541">
       <c r="A541" t="str">
@@ -29071,6 +30535,9 @@
       <c r="Q541" t="b">
         <v>1</v>
       </c>
+      <c r="R541" t="str">
+        <v>XPS.L</v>
+      </c>
     </row>
     <row r="542">
       <c r="A542" t="str">
@@ -29124,6 +30591,9 @@
       <c r="Q542" t="b">
         <v>0</v>
       </c>
+      <c r="R542" t="str">
+        <v>3SQ1.F</v>
+      </c>
     </row>
     <row r="543">
       <c r="A543" t="str">
@@ -29177,6 +30647,9 @@
       <c r="Q543" t="b">
         <v>1</v>
       </c>
+      <c r="R543" t="str">
+        <v>ABNX.PA</v>
+      </c>
     </row>
     <row r="544">
       <c r="A544" t="str">
@@ -29283,6 +30756,9 @@
       <c r="Q545" t="b">
         <v>1</v>
       </c>
+      <c r="R545" t="str">
+        <v>ADZ.MC</v>
+      </c>
     </row>
     <row r="546">
       <c r="A546" t="str">
@@ -29336,6 +30812,9 @@
       <c r="Q546" t="b">
         <v>1</v>
       </c>
+      <c r="R546" t="str">
+        <v>AENA.MC</v>
+      </c>
     </row>
     <row r="547">
       <c r="A547" t="str">
@@ -29389,6 +30868,9 @@
       <c r="Q547" t="b">
         <v>0</v>
       </c>
+      <c r="R547" t="str">
+        <v>ALAGR.PA</v>
+      </c>
     </row>
     <row r="548">
       <c r="A548" t="str">
@@ -29442,6 +30924,9 @@
       <c r="Q548" t="b">
         <v>0</v>
       </c>
+      <c r="R548" t="str">
+        <v>ALB.MU</v>
+      </c>
     </row>
     <row r="549">
       <c r="A549" t="str">
@@ -29495,6 +30980,9 @@
       <c r="Q549" t="b">
         <v>1</v>
       </c>
+      <c r="R549" t="str">
+        <v>ACT.DE</v>
+      </c>
     </row>
     <row r="550">
       <c r="A550" t="str">
@@ -29548,6 +31036,9 @@
       <c r="Q550" t="b">
         <v>0</v>
       </c>
+      <c r="R550" t="str">
+        <v>ATSI.MC</v>
+      </c>
     </row>
     <row r="551">
       <c r="A551" t="str">
@@ -29601,6 +31092,9 @@
       <c r="Q551" t="b">
         <v>0</v>
       </c>
+      <c r="R551" t="str">
+        <v>ALAQU.PA</v>
+      </c>
     </row>
     <row r="552">
       <c r="A552" t="str">
@@ -29654,6 +31148,9 @@
       <c r="Q552" t="b">
         <v>1</v>
       </c>
+      <c r="R552" t="str">
+        <v>ART.MC</v>
+      </c>
     </row>
     <row r="553">
       <c r="A553" t="str">
@@ -29707,6 +31204,9 @@
       <c r="Q553" t="b">
         <v>0</v>
       </c>
+      <c r="R553" t="str">
+        <v>3ITN.DE</v>
+      </c>
     </row>
     <row r="554">
       <c r="A554" t="str">
@@ -29760,6 +31260,9 @@
       <c r="Q554" t="b">
         <v>0</v>
       </c>
+      <c r="R554" t="str">
+        <v>ORA.TO</v>
+      </c>
     </row>
     <row r="555">
       <c r="A555" t="str">
@@ -29813,6 +31316,9 @@
       <c r="Q555" t="b">
         <v>0</v>
       </c>
+      <c r="R555" t="str">
+        <v>3D6.DE</v>
+      </c>
     </row>
     <row r="556">
       <c r="A556" t="str">
@@ -29866,6 +31372,9 @@
       <c r="Q556" t="b">
         <v>1</v>
       </c>
+      <c r="R556" t="str">
+        <v>AZK.MC</v>
+      </c>
     </row>
     <row r="557">
       <c r="A557" t="str">
@@ -29919,6 +31428,9 @@
       <c r="Q557" t="b">
         <v>1</v>
       </c>
+      <c r="R557" t="str">
+        <v>BALYO.PA</v>
+      </c>
     </row>
     <row r="558">
       <c r="A558" t="str">
@@ -29972,6 +31484,9 @@
       <c r="Q558" t="b">
         <v>1</v>
       </c>
+      <c r="R558" t="str">
+        <v>BEZ.DE</v>
+      </c>
     </row>
     <row r="559">
       <c r="A559" t="str">
@@ -30025,6 +31540,9 @@
       <c r="Q559" t="b">
         <v>0</v>
       </c>
+      <c r="R559" t="str">
+        <v>BFV.F</v>
+      </c>
     </row>
     <row r="560">
       <c r="A560" t="str">
@@ -30078,6 +31596,9 @@
       <c r="Q560" t="b">
         <v>0</v>
       </c>
+      <c r="R560" t="str">
+        <v>SPT6.F</v>
+      </c>
     </row>
     <row r="561">
       <c r="A561" t="str">
@@ -30131,6 +31652,9 @@
       <c r="Q561" t="b">
         <v>0</v>
       </c>
+      <c r="R561" t="str">
+        <v>BHSC.CN</v>
+      </c>
     </row>
     <row r="562">
       <c r="A562" t="str">
@@ -30184,6 +31708,9 @@
       <c r="Q562" t="b">
         <v>0</v>
       </c>
+      <c r="R562" t="str">
+        <v>ALBOA.PA</v>
+      </c>
     </row>
     <row r="563">
       <c r="A563" t="str">
@@ -30237,6 +31764,9 @@
       <c r="Q563" t="b">
         <v>1</v>
       </c>
+      <c r="R563" t="str">
+        <v>BSD.PA</v>
+      </c>
     </row>
     <row r="564">
       <c r="A564" t="str">
@@ -30290,6 +31820,9 @@
       <c r="Q564" t="b">
         <v>1</v>
       </c>
+      <c r="R564" t="str">
+        <v>CAP.PA</v>
+      </c>
     </row>
     <row r="565">
       <c r="A565" t="str">
@@ -30343,6 +31876,9 @@
       <c r="Q565" t="b">
         <v>0</v>
       </c>
+      <c r="R565" t="str">
+        <v>CTNK.F</v>
+      </c>
     </row>
     <row r="566">
       <c r="A566" t="str">
@@ -30396,6 +31932,9 @@
       <c r="Q566" t="b">
         <v>1</v>
       </c>
+      <c r="R566" t="str">
+        <v>CEK.DE</v>
+      </c>
     </row>
     <row r="567">
       <c r="A567" t="str">
@@ -30449,6 +31988,9 @@
       <c r="Q567" t="b">
         <v>0</v>
       </c>
+      <c r="R567" t="str">
+        <v>CMTL.MI</v>
+      </c>
     </row>
     <row r="568">
       <c r="A568" t="str">
@@ -30502,6 +32044,9 @@
       <c r="Q568" t="b">
         <v>1</v>
       </c>
+      <c r="R568" t="str">
+        <v>DIS.MI</v>
+      </c>
     </row>
     <row r="569">
       <c r="A569" t="str">
@@ -30555,6 +32100,9 @@
       <c r="Q569" t="b">
         <v>0</v>
       </c>
+      <c r="R569" t="str">
+        <v>DWB.SG</v>
+      </c>
     </row>
     <row r="570">
       <c r="A570" t="str">
@@ -30608,6 +32156,9 @@
       <c r="Q570" t="b">
         <v>0</v>
       </c>
+      <c r="R570" t="str">
+        <v>ALDNX.PA</v>
+      </c>
     </row>
     <row r="571">
       <c r="A571" t="str">
@@ -30661,6 +32212,9 @@
       <c r="Q571" t="b">
         <v>0</v>
       </c>
+      <c r="R571" t="str">
+        <v>DOT.MI</v>
+      </c>
     </row>
     <row r="572">
       <c r="A572" t="str">
@@ -30714,6 +32268,9 @@
       <c r="Q572" t="b">
         <v>0</v>
       </c>
+      <c r="R572" t="str">
+        <v>ALDRV.PA</v>
+      </c>
     </row>
     <row r="573">
       <c r="A573" t="str">
@@ -30767,6 +32324,9 @@
       <c r="Q573" t="b">
         <v>0</v>
       </c>
+      <c r="R573" t="str">
+        <v>ELB.MI</v>
+      </c>
     </row>
     <row r="574">
       <c r="A574" t="str">
@@ -30820,6 +32380,9 @@
       <c r="Q574" t="b">
         <v>1</v>
       </c>
+      <c r="R574" t="str">
+        <v>ENO.MC</v>
+      </c>
     </row>
     <row r="575">
       <c r="A575" t="str">
@@ -30873,6 +32436,9 @@
       <c r="Q575" t="b">
         <v>0</v>
       </c>
+      <c r="R575" t="str">
+        <v>ALDUB.PA</v>
+      </c>
     </row>
     <row r="576">
       <c r="A576" t="str">
@@ -30926,6 +32492,9 @@
       <c r="Q576" t="b">
         <v>0</v>
       </c>
+      <c r="R576" t="str">
+        <v>ET.MI</v>
+      </c>
     </row>
     <row r="577">
       <c r="A577" t="str">
@@ -30979,6 +32548,9 @@
       <c r="Q577" t="b">
         <v>0</v>
       </c>
+      <c r="R577" t="str">
+        <v>ALERS.PA</v>
+      </c>
     </row>
     <row r="578">
       <c r="A578" t="str">
@@ -31032,6 +32604,9 @@
       <c r="Q578" t="b">
         <v>0</v>
       </c>
+      <c r="R578" t="str">
+        <v>FHW.F</v>
+      </c>
     </row>
     <row r="579">
       <c r="A579" t="str">
@@ -31085,6 +32660,9 @@
       <c r="Q579" t="b">
         <v>0</v>
       </c>
+      <c r="R579" t="str">
+        <v>FRS.DE</v>
+      </c>
     </row>
     <row r="580">
       <c r="A580" t="str">
@@ -31138,6 +32716,9 @@
       <c r="Q580" t="b">
         <v>1</v>
       </c>
+      <c r="R580" t="str">
+        <v>FQT.DE</v>
+      </c>
     </row>
     <row r="581">
       <c r="A581" t="str">
@@ -31191,6 +32772,9 @@
       <c r="Q581" t="b">
         <v>0</v>
       </c>
+      <c r="R581" t="str">
+        <v>NLM.F</v>
+      </c>
     </row>
     <row r="582">
       <c r="A582" t="str">
@@ -31244,6 +32828,9 @@
       <c r="Q582" t="b">
         <v>0</v>
       </c>
+      <c r="R582" t="str">
+        <v>FEW.F</v>
+      </c>
     </row>
     <row r="583">
       <c r="A583" t="str">
@@ -31294,6 +32881,12 @@
       <c r="P583" t="str">
         <v>Add</v>
       </c>
+      <c r="Q583" t="b">
+        <v>0</v>
+      </c>
+      <c r="R583" t="str">
+        <v>WWG.F</v>
+      </c>
     </row>
     <row r="584">
       <c r="A584" t="str">
@@ -31344,6 +32937,12 @@
       <c r="P584" t="str">
         <v>Add</v>
       </c>
+      <c r="Q584" t="b">
+        <v>1</v>
+      </c>
+      <c r="R584" t="str">
+        <v>GNFT.PA</v>
+      </c>
     </row>
     <row r="585">
       <c r="A585" t="str">
@@ -31394,6 +32993,12 @@
       <c r="P585" t="str">
         <v>Add</v>
       </c>
+      <c r="Q585" t="b">
+        <v>1</v>
+      </c>
+      <c r="R585" t="str">
+        <v>SIGHT.PA</v>
+      </c>
     </row>
     <row r="586">
       <c r="A586" t="str">
@@ -31444,6 +33049,12 @@
       <c r="P586" t="str">
         <v>Add</v>
       </c>
+      <c r="Q586" t="b">
+        <v>1</v>
+      </c>
+      <c r="R586" t="str">
+        <v>GM.MI</v>
+      </c>
     </row>
     <row r="587">
       <c r="A587" t="str">
@@ -31494,6 +33105,12 @@
       <c r="P587" t="str">
         <v>Add</v>
       </c>
+      <c r="Q587" t="b">
+        <v>1</v>
+      </c>
+      <c r="R587" t="str">
+        <v>GSC1.DE</v>
+      </c>
     </row>
     <row r="588">
       <c r="A588" t="str">
@@ -31544,6 +33161,12 @@
       <c r="P588" t="str">
         <v>Add</v>
       </c>
+      <c r="Q588" t="b">
+        <v>1</v>
+      </c>
+      <c r="R588" t="str">
+        <v>GEA.PA</v>
+      </c>
     </row>
     <row r="589">
       <c r="A589" t="str">
@@ -31594,6 +33217,12 @@
       <c r="P589" t="str">
         <v>Add</v>
       </c>
+      <c r="Q589" t="b">
+        <v>1</v>
+      </c>
+      <c r="R589" t="str">
+        <v>GSJ.MC</v>
+      </c>
     </row>
     <row r="590">
       <c r="A590" t="str">
@@ -31644,6 +33273,12 @@
       <c r="P590" t="str">
         <v>Add</v>
       </c>
+      <c r="Q590" t="b">
+        <v>0</v>
+      </c>
+      <c r="R590" t="str">
+        <v>EZE.MC</v>
+      </c>
     </row>
     <row r="591">
       <c r="A591" t="str">
@@ -31694,6 +33329,12 @@
       <c r="P591" t="str">
         <v>Add</v>
       </c>
+      <c r="Q591" t="b">
+        <v>1</v>
+      </c>
+      <c r="R591" t="str">
+        <v>GVS.MI</v>
+      </c>
     </row>
     <row r="592">
       <c r="A592" t="str">
@@ -31744,6 +33385,12 @@
       <c r="P592" t="str">
         <v>Add</v>
       </c>
+      <c r="Q592" t="b">
+        <v>1</v>
+      </c>
+      <c r="R592" t="str">
+        <v>HAG.DE</v>
+      </c>
     </row>
     <row r="593">
       <c r="A593" t="str">
@@ -31794,6 +33441,12 @@
       <c r="P593" t="str">
         <v>Add</v>
       </c>
+      <c r="Q593" t="b">
+        <v>0</v>
+      </c>
+      <c r="R593" t="str">
+        <v>HMU.DE</v>
+      </c>
     </row>
     <row r="594">
       <c r="A594" t="str">
@@ -31844,6 +33497,12 @@
       <c r="P594" t="str">
         <v>Add</v>
       </c>
+      <c r="Q594" t="b">
+        <v>0</v>
+      </c>
+      <c r="R594" t="str">
+        <v>ICOP.MI</v>
+      </c>
     </row>
     <row r="595">
       <c r="A595" t="str">
@@ -31894,6 +33553,12 @@
       <c r="P595" t="str">
         <v>Add</v>
       </c>
+      <c r="Q595" t="b">
+        <v>0</v>
+      </c>
+      <c r="R595" t="str">
+        <v>IBU.DE</v>
+      </c>
     </row>
     <row r="596">
       <c r="A596" t="str">
@@ -31944,6 +33609,12 @@
       <c r="P596" t="str">
         <v>Add</v>
       </c>
+      <c r="Q596" t="b">
+        <v>0</v>
+      </c>
+      <c r="R596" t="str">
+        <v>IFLEX.MC</v>
+      </c>
     </row>
     <row r="597">
       <c r="A597" t="str">
@@ -31994,6 +33665,12 @@
       <c r="P597" t="str">
         <v>Add</v>
       </c>
+      <c r="Q597" t="b">
+        <v>0</v>
+      </c>
+      <c r="R597" t="str">
+        <v>MPT.MI</v>
+      </c>
     </row>
     <row r="598">
       <c r="A598" t="str">
@@ -32044,6 +33721,12 @@
       <c r="P598" t="str">
         <v>Add</v>
       </c>
+      <c r="Q598" t="b">
+        <v>0</v>
+      </c>
+      <c r="R598" t="str">
+        <v>1INN.MU</v>
+      </c>
     </row>
     <row r="599">
       <c r="A599" t="str">
@@ -32094,6 +33777,12 @@
       <c r="P599" t="str">
         <v>Add</v>
       </c>
+      <c r="Q599" t="b">
+        <v>0</v>
+      </c>
+      <c r="R599" t="str">
+        <v>TSS.F</v>
+      </c>
     </row>
     <row r="600">
       <c r="A600" t="str">
@@ -32144,6 +33833,12 @@
       <c r="P600" t="str">
         <v>Add</v>
       </c>
+      <c r="Q600" t="b">
+        <v>1</v>
+      </c>
+      <c r="R600" t="str">
+        <v>IOS.DE</v>
+      </c>
     </row>
     <row r="601">
       <c r="A601" t="str">
@@ -32194,6 +33889,12 @@
       <c r="P601" t="str">
         <v>Add</v>
       </c>
+      <c r="Q601" t="b">
+        <v>1</v>
+      </c>
+      <c r="R601" t="str">
+        <v>KBX.DE</v>
+      </c>
     </row>
     <row r="602">
       <c r="A602" t="str">
@@ -32244,6 +33945,12 @@
       <c r="P602" t="str">
         <v>Add</v>
       </c>
+      <c r="Q602" t="b">
+        <v>1</v>
+      </c>
+      <c r="R602" t="str">
+        <v>KTN.DE</v>
+      </c>
     </row>
     <row r="603">
       <c r="A603" t="str">
@@ -32294,6 +34001,12 @@
       <c r="P603" t="str">
         <v>Add</v>
       </c>
+      <c r="Q603" t="b">
+        <v>1</v>
+      </c>
+      <c r="R603" t="str">
+        <v>KRN.DE</v>
+      </c>
     </row>
     <row r="604">
       <c r="A604" t="str">
@@ -32344,6 +34057,12 @@
       <c r="P604" t="str">
         <v>Add</v>
       </c>
+      <c r="Q604" t="b">
+        <v>0</v>
+      </c>
+      <c r="R604" t="str">
+        <v>ALVAP.PA</v>
+      </c>
     </row>
     <row r="605">
       <c r="A605" t="str">
@@ -32394,6 +34113,12 @@
       <c r="P605" t="str">
         <v>Add</v>
       </c>
+      <c r="Q605" t="b">
+        <v>0</v>
+      </c>
+      <c r="R605" t="str">
+        <v>LEC.F</v>
+      </c>
     </row>
     <row r="606">
       <c r="A606" t="str">
@@ -32444,6 +34169,12 @@
       <c r="P606" t="str">
         <v>Add</v>
       </c>
+      <c r="Q606" t="b">
+        <v>1</v>
+      </c>
+      <c r="R606" t="str">
+        <v>LDO.MI</v>
+      </c>
     </row>
     <row r="607">
       <c r="A607" t="str">
@@ -32494,6 +34225,12 @@
       <c r="P607" t="str">
         <v>Add</v>
       </c>
+      <c r="Q607" t="b">
+        <v>1</v>
+      </c>
+      <c r="R607" t="str">
+        <v>MALT.PA</v>
+      </c>
     </row>
     <row r="608">
       <c r="A608" t="str">
@@ -32544,6 +34281,12 @@
       <c r="P608" t="str">
         <v>Add</v>
       </c>
+      <c r="Q608" t="b">
+        <v>0</v>
+      </c>
+      <c r="R608" t="str">
+        <v>MAPS.MI</v>
+      </c>
     </row>
     <row r="609">
       <c r="A609" t="str">
@@ -32594,6 +34337,12 @@
       <c r="P609" t="str">
         <v>Add</v>
       </c>
+      <c r="Q609" t="b">
+        <v>0</v>
+      </c>
+      <c r="R609" t="str">
+        <v>MARK.MI</v>
+      </c>
     </row>
     <row r="610">
       <c r="A610" t="str">
@@ -32644,6 +34393,12 @@
       <c r="P610" t="str">
         <v>Add</v>
       </c>
+      <c r="Q610" t="b">
+        <v>0</v>
+      </c>
+      <c r="R610" t="str">
+        <v>MBH3.F</v>
+      </c>
     </row>
     <row r="611">
       <c r="A611" t="str">
@@ -32694,6 +34449,12 @@
       <c r="P611" t="str">
         <v>Add</v>
       </c>
+      <c r="Q611" t="b">
+        <v>0</v>
+      </c>
+      <c r="R611" t="str">
+        <v>MAK.DE</v>
+      </c>
     </row>
     <row r="612">
       <c r="A612" t="str">
@@ -32744,6 +34505,12 @@
       <c r="P612" t="str">
         <v>Add</v>
       </c>
+      <c r="Q612" t="b">
+        <v>0</v>
+      </c>
+      <c r="R612" t="str">
+        <v>MFT.MI</v>
+      </c>
     </row>
     <row r="613">
       <c r="A613" t="str">
@@ -32794,6 +34561,12 @@
       <c r="P613" t="str">
         <v>Add</v>
       </c>
+      <c r="Q613" t="b">
+        <v>0</v>
+      </c>
+      <c r="R613" t="str">
+        <v>MTK.MI</v>
+      </c>
     </row>
     <row r="614">
       <c r="A614" t="str">
@@ -32844,6 +34617,12 @@
       <c r="P614" t="str">
         <v>Add</v>
       </c>
+      <c r="Q614" t="b">
+        <v>1</v>
+      </c>
+      <c r="R614" t="str">
+        <v>MVC.MC</v>
+      </c>
     </row>
     <row r="615">
       <c r="A615" t="str">
@@ -32894,6 +34673,12 @@
       <c r="P615" t="str">
         <v>Add</v>
       </c>
+      <c r="Q615" t="b">
+        <v>1</v>
+      </c>
+      <c r="R615" t="str">
+        <v>MRX.DE</v>
+      </c>
     </row>
     <row r="616">
       <c r="A616" t="str">
@@ -32944,6 +34729,12 @@
       <c r="P616" t="str">
         <v>Add</v>
       </c>
+      <c r="Q616" t="b">
+        <v>0</v>
+      </c>
+      <c r="R616" t="str">
+        <v>MSAG.DE</v>
+      </c>
     </row>
     <row r="617">
       <c r="A617" t="str">
@@ -32994,6 +34785,12 @@
       <c r="P617" t="str">
         <v>Add</v>
       </c>
+      <c r="Q617" t="b">
+        <v>0</v>
+      </c>
+      <c r="R617" t="str">
+        <v>NAT.MC</v>
+      </c>
     </row>
     <row r="618">
       <c r="A618" t="str">
@@ -33044,6 +34841,12 @@
       <c r="P618" t="str">
         <v>Add</v>
       </c>
+      <c r="Q618" t="b">
+        <v>0</v>
+      </c>
+      <c r="R618" t="str">
+        <v>ALNOV.PA</v>
+      </c>
     </row>
     <row r="619">
       <c r="A619" t="str">
@@ -33094,6 +34897,12 @@
       <c r="P619" t="str">
         <v>Add</v>
       </c>
+      <c r="Q619" t="b">
+        <v>0</v>
+      </c>
+      <c r="R619" t="str">
+        <v>ALNSE.PA</v>
+      </c>
     </row>
     <row r="620">
       <c r="A620" t="str">
@@ -33144,6 +34953,12 @@
       <c r="P620" t="str">
         <v>Add</v>
       </c>
+      <c r="Q620" t="b">
+        <v>1</v>
+      </c>
+      <c r="R620" t="str">
+        <v>NXT.MC</v>
+      </c>
     </row>
     <row r="621">
       <c r="A621" t="str">
@@ -33194,6 +35009,12 @@
       <c r="P621" t="str">
         <v>Add</v>
       </c>
+      <c r="Q621" t="b">
+        <v>1</v>
+      </c>
+      <c r="R621" t="str">
+        <v>SBT.PA</v>
+      </c>
     </row>
     <row r="622">
       <c r="A622" t="str">
@@ -33244,6 +35065,12 @@
       <c r="P622" t="str">
         <v>Add</v>
       </c>
+      <c r="Q622" t="b">
+        <v>1</v>
+      </c>
+      <c r="R622" t="str">
+        <v>OHB.DE</v>
+      </c>
     </row>
     <row r="623">
       <c r="A623" t="str">
@@ -33294,6 +35121,12 @@
       <c r="P623" t="str">
         <v>Add</v>
       </c>
+      <c r="Q623" t="b">
+        <v>0</v>
+      </c>
+      <c r="R623" t="str">
+        <v>ALEXP.PA</v>
+      </c>
     </row>
     <row r="624">
       <c r="A624" t="str">
@@ -33344,6 +35177,12 @@
       <c r="P624" t="str">
         <v>Add</v>
       </c>
+      <c r="Q624" t="b">
+        <v>0</v>
+      </c>
+      <c r="R624" t="str">
+        <v>OPTS.MC</v>
+      </c>
     </row>
     <row r="625">
       <c r="A625" t="str">
@@ -33394,6 +35233,12 @@
       <c r="P625" t="str">
         <v>Add</v>
       </c>
+      <c r="Q625" t="b">
+        <v>0</v>
+      </c>
+      <c r="R625" t="str">
+        <v>OTO.MI</v>
+      </c>
     </row>
     <row r="626">
       <c r="A626" t="str">
@@ -33444,6 +35289,12 @@
       <c r="P626" t="str">
         <v>Add</v>
       </c>
+      <c r="Q626" t="b">
+        <v>1</v>
+      </c>
+      <c r="R626" t="str">
+        <v>OVS.MI</v>
+      </c>
     </row>
     <row r="627">
       <c r="A627" t="str">
@@ -33494,6 +35345,12 @@
       <c r="P627" t="str">
         <v>Add</v>
       </c>
+      <c r="Q627" t="b">
+        <v>0</v>
+      </c>
+      <c r="R627" t="str">
+        <v>PEH.F</v>
+      </c>
     </row>
     <row r="628">
       <c r="A628" t="str">
@@ -33544,6 +35401,12 @@
       <c r="P628" t="str">
         <v>Add</v>
       </c>
+      <c r="Q628" t="b">
+        <v>1</v>
+      </c>
+      <c r="R628" t="str">
+        <v>PFSE.DE</v>
+      </c>
     </row>
     <row r="629">
       <c r="A629" t="str">
@@ -33594,6 +35457,12 @@
       <c r="P629" t="str">
         <v>Add</v>
       </c>
+      <c r="Q629" t="b">
+        <v>0</v>
+      </c>
+      <c r="R629" t="str">
+        <v>PLEK.F</v>
+      </c>
     </row>
     <row r="630">
       <c r="A630" t="str">
@@ -33644,6 +35513,12 @@
       <c r="P630" t="str">
         <v>Add</v>
       </c>
+      <c r="Q630" t="b">
+        <v>0</v>
+      </c>
+      <c r="R630" t="str">
+        <v>ALPRE.PA</v>
+      </c>
     </row>
     <row r="631">
       <c r="A631" t="str">
@@ -33694,6 +35569,12 @@
       <c r="P631" t="str">
         <v>Add</v>
       </c>
+      <c r="Q631" t="b">
+        <v>1</v>
+      </c>
+      <c r="R631" t="str">
+        <v>PRY.MI</v>
+      </c>
     </row>
     <row r="632">
       <c r="A632" t="str">
@@ -33744,6 +35625,9 @@
       <c r="P632" t="str">
         <v>Add</v>
       </c>
+      <c r="Q632" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="633">
       <c r="A633" t="str">
@@ -33794,6 +35678,12 @@
       <c r="P633" t="str">
         <v>Add</v>
       </c>
+      <c r="Q633" t="b">
+        <v>0</v>
+      </c>
+      <c r="R633" t="str">
+        <v>RNV.MI</v>
+      </c>
     </row>
     <row r="634">
       <c r="A634" t="str">
@@ -33844,6 +35734,12 @@
       <c r="P634" t="str">
         <v>Add</v>
       </c>
+      <c r="Q634" t="b">
+        <v>1</v>
+      </c>
+      <c r="R634" t="str">
+        <v>RN.MI</v>
+      </c>
     </row>
     <row r="635">
       <c r="A635" t="str">
@@ -33894,6 +35790,12 @@
       <c r="P635" t="str">
         <v>Add</v>
       </c>
+      <c r="Q635" t="b">
+        <v>0</v>
+      </c>
+      <c r="R635" t="str">
+        <v>ALROC.PA</v>
+      </c>
     </row>
     <row r="636">
       <c r="A636" t="str">
@@ -33944,6 +35846,12 @@
       <c r="P636" t="str">
         <v>Add</v>
       </c>
+      <c r="Q636" t="b">
+        <v>0</v>
+      </c>
+      <c r="R636" t="str">
+        <v>ALSMA.PA</v>
+      </c>
     </row>
     <row r="637">
       <c r="A637" t="str">
@@ -33994,6 +35902,9 @@
       <c r="P637" t="str">
         <v>Add</v>
       </c>
+      <c r="Q637" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="638">
       <c r="A638" t="str">
@@ -34044,6 +35955,9 @@
       <c r="P638" t="str">
         <v>Add</v>
       </c>
+      <c r="Q638" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="639">
       <c r="A639" t="str">
@@ -34094,6 +36008,12 @@
       <c r="P639" t="str">
         <v>Add</v>
       </c>
+      <c r="Q639" t="b">
+        <v>0</v>
+      </c>
+      <c r="R639" t="str">
+        <v>CY1K.F</v>
+      </c>
     </row>
     <row r="640">
       <c r="A640" t="str">
@@ -34144,6 +36064,12 @@
       <c r="P640" t="str">
         <v>Add</v>
       </c>
+      <c r="Q640" t="b">
+        <v>0</v>
+      </c>
+      <c r="R640" t="str">
+        <v>SSS.DU</v>
+      </c>
     </row>
     <row r="641">
       <c r="A641" t="str">
@@ -34194,6 +36120,12 @@
       <c r="P641" t="str">
         <v>Add</v>
       </c>
+      <c r="Q641" t="b">
+        <v>0</v>
+      </c>
+      <c r="R641" t="str">
+        <v>ALSEM.PA</v>
+      </c>
     </row>
     <row r="642">
       <c r="A642" t="str">
@@ -34244,6 +36176,12 @@
       <c r="P642" t="str">
         <v>Add</v>
       </c>
+      <c r="Q642" t="b">
+        <v>0</v>
+      </c>
+      <c r="R642" t="str">
+        <v>SCO.MC</v>
+      </c>
     </row>
     <row r="643">
       <c r="A643" t="str">
@@ -34294,6 +36232,12 @@
       <c r="P643" t="str">
         <v>Add</v>
       </c>
+      <c r="Q643" t="b">
+        <v>1</v>
+      </c>
+      <c r="R643" t="str">
+        <v>SJJ.DE</v>
+      </c>
     </row>
     <row r="644">
       <c r="A644" t="str">
@@ -34344,6 +36288,12 @@
       <c r="P644" t="str">
         <v>Add</v>
       </c>
+      <c r="Q644" t="b">
+        <v>0</v>
+      </c>
+      <c r="R644" t="str">
+        <v>SNG.MC</v>
+      </c>
     </row>
     <row r="645">
       <c r="A645" t="str">
@@ -34394,6 +36344,12 @@
       <c r="P645" t="str">
         <v>Add</v>
       </c>
+      <c r="Q645" t="b">
+        <v>0</v>
+      </c>
+      <c r="R645" t="str">
+        <v>SB1.DE</v>
+      </c>
     </row>
     <row r="646">
       <c r="A646" t="str">
@@ -34444,6 +36400,12 @@
       <c r="P646" t="str">
         <v>Add</v>
       </c>
+      <c r="Q646" t="b">
+        <v>1</v>
+      </c>
+      <c r="R646" t="str">
+        <v>SHF.DE</v>
+      </c>
     </row>
     <row r="647">
       <c r="A647" t="str">
@@ -34494,6 +36456,12 @@
       <c r="P647" t="str">
         <v>Add</v>
       </c>
+      <c r="Q647" t="b">
+        <v>1</v>
+      </c>
+      <c r="R647" t="str">
+        <v>EXPL.PA</v>
+      </c>
     </row>
     <row r="648">
       <c r="A648" t="str">
@@ -34544,6 +36512,12 @@
       <c r="P648" t="str">
         <v>Add</v>
       </c>
+      <c r="Q648" t="b">
+        <v>1</v>
+      </c>
+      <c r="R648" t="str">
+        <v>SYT.DE</v>
+      </c>
     </row>
     <row r="649">
       <c r="A649" t="str">
@@ -34594,6 +36568,12 @@
       <c r="P649" t="str">
         <v>Add</v>
       </c>
+      <c r="Q649" t="b">
+        <v>1</v>
+      </c>
+      <c r="R649" t="str">
+        <v>SFT.MI</v>
+      </c>
     </row>
     <row r="650">
       <c r="A650" t="str">
@@ -34644,6 +36624,12 @@
       <c r="P650" t="str">
         <v>Add</v>
       </c>
+      <c r="Q650" t="b">
+        <v>0</v>
+      </c>
+      <c r="R650" t="str">
+        <v>SPN.MI</v>
+      </c>
     </row>
     <row r="651">
       <c r="A651" t="str">
@@ -34694,6 +36680,12 @@
       <c r="P651" t="str">
         <v>Add</v>
       </c>
+      <c r="Q651" t="b">
+        <v>0</v>
+      </c>
+      <c r="R651" t="str">
+        <v>ALSPW.PA</v>
+      </c>
     </row>
     <row r="652">
       <c r="A652" t="str">
@@ -34744,6 +36736,12 @@
       <c r="P652" t="str">
         <v>Add</v>
       </c>
+      <c r="Q652" t="b">
+        <v>0</v>
+      </c>
+      <c r="R652" t="str">
+        <v>4X0.DE</v>
+      </c>
     </row>
     <row r="653">
       <c r="A653" t="str">
@@ -34794,6 +36792,12 @@
       <c r="P653" t="str">
         <v>Add</v>
       </c>
+      <c r="Q653" t="b">
+        <v>1</v>
+      </c>
+      <c r="R653" t="str">
+        <v>TVRB.PA</v>
+      </c>
     </row>
     <row r="654">
       <c r="A654" t="str">
@@ -34844,6 +36848,12 @@
       <c r="P654" t="str">
         <v>Add</v>
       </c>
+      <c r="Q654" t="b">
+        <v>1</v>
+      </c>
+      <c r="R654" t="str">
+        <v>TKMS.DE</v>
+      </c>
     </row>
     <row r="655">
       <c r="A655" t="str">
@@ -34894,6 +36904,12 @@
       <c r="P655" t="str">
         <v>Add</v>
       </c>
+      <c r="Q655" t="b">
+        <v>0</v>
+      </c>
+      <c r="R655" t="str">
+        <v>TMP.MI</v>
+      </c>
     </row>
     <row r="656">
       <c r="A656" t="str">
@@ -34944,6 +36960,12 @@
       <c r="P656" t="str">
         <v>Add</v>
       </c>
+      <c r="Q656" t="b">
+        <v>0</v>
+      </c>
+      <c r="R656" t="str">
+        <v>TPS.MI</v>
+      </c>
     </row>
     <row r="657">
       <c r="A657" t="str">
@@ -34994,6 +37016,9 @@
       <c r="P657" t="str">
         <v>Add</v>
       </c>
+      <c r="Q657" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="658">
       <c r="A658" t="str">
@@ -35044,6 +37069,12 @@
       <c r="P658" t="str">
         <v>Add</v>
       </c>
+      <c r="Q658" t="b">
+        <v>0</v>
+      </c>
+      <c r="R658" t="str">
+        <v>TRAI.MI</v>
+      </c>
     </row>
     <row r="659">
       <c r="A659" t="str">
@@ -35094,6 +37125,12 @@
       <c r="P659" t="str">
         <v>Add</v>
       </c>
+      <c r="Q659" t="b">
+        <v>0</v>
+      </c>
+      <c r="R659" t="str">
+        <v>ALTRI.PA</v>
+      </c>
     </row>
     <row r="660">
       <c r="A660" t="str">
@@ -35144,6 +37181,12 @@
       <c r="P660" t="str">
         <v>Add</v>
       </c>
+      <c r="Q660" t="b">
+        <v>0</v>
+      </c>
+      <c r="R660" t="str">
+        <v>TUR.F</v>
+      </c>
     </row>
     <row r="661">
       <c r="A661" t="str">
@@ -35194,6 +37237,12 @@
       <c r="P661" t="str">
         <v>Add</v>
       </c>
+      <c r="Q661" t="b">
+        <v>0</v>
+      </c>
+      <c r="R661" t="str">
+        <v>ALTXC.PA</v>
+      </c>
     </row>
     <row r="662">
       <c r="A662" t="str">
@@ -35244,6 +37293,12 @@
       <c r="P662" t="str">
         <v>Add</v>
       </c>
+      <c r="Q662" t="b">
+        <v>0</v>
+      </c>
+      <c r="R662" t="str">
+        <v>ALVAL.PA</v>
+      </c>
     </row>
     <row r="663">
       <c r="A663" t="str">
@@ -35294,6 +37349,12 @@
       <c r="P663" t="str">
         <v>Add</v>
       </c>
+      <c r="Q663" t="b">
+        <v>0</v>
+      </c>
+      <c r="R663" t="str">
+        <v>ALVU.PA</v>
+      </c>
     </row>
     <row r="664">
       <c r="A664" t="str">
@@ -35344,6 +37405,12 @@
       <c r="P664" t="str">
         <v>Add</v>
       </c>
+      <c r="Q664" t="b">
+        <v>0</v>
+      </c>
+      <c r="R664" t="str">
+        <v>ALVIA.PA</v>
+      </c>
     </row>
     <row r="665">
       <c r="A665" t="str">
@@ -35394,6 +37461,12 @@
       <c r="P665" t="str">
         <v>Add</v>
       </c>
+      <c r="Q665" t="b">
+        <v>1</v>
+      </c>
+      <c r="R665" t="str">
+        <v>VID.MC</v>
+      </c>
     </row>
     <row r="666">
       <c r="A666" t="str">
@@ -35444,6 +37517,12 @@
       <c r="P666" t="str">
         <v>Add</v>
       </c>
+      <c r="Q666" t="b">
+        <v>0</v>
+      </c>
+      <c r="R666" t="str">
+        <v>VNXT.MI</v>
+      </c>
     </row>
     <row r="667">
       <c r="A667" t="str">
@@ -35494,6 +37573,12 @@
       <c r="P667" t="str">
         <v>Add</v>
       </c>
+      <c r="Q667" t="b">
+        <v>1</v>
+      </c>
+      <c r="R667" t="str">
+        <v>WAC.DE</v>
+      </c>
     </row>
     <row r="668">
       <c r="A668" t="str">
@@ -35543,6 +37628,12 @@
       </c>
       <c r="P668" t="str">
         <v>Add</v>
+      </c>
+      <c r="Q668" t="b">
+        <v>1</v>
+      </c>
+      <c r="R668" t="str">
+        <v>ZV.MI</v>
       </c>
     </row>
   </sheetData>
